--- a/Research/Instructions/Ricoh 5A22 Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Ricoh 5A22 Instructions Emulation SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB12AD5-379C-479C-AF8D-EA4F9517F9CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FEE5B5-15AA-40C4-BE9A-9C7689BF4152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6331" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6332" uniqueCount="588">
   <si>
     <t>BRK (00)</t>
   </si>
@@ -11030,6 +11030,110 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Set the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag to 1.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag to 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag to 1.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag to 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Set Operand.L to </t>
     </r>
     <r>
@@ -11041,6 +11145,163 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flags set.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H to 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>A</t>
     </r>
     <r>
@@ -11051,10 +11312,2186 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve">.L and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H to 1.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L by 3 and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H to 1.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L by 1 and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H to 1.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L by 2 and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H to 1.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L by 2 and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H to 1. Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = Address.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L by 3 and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H to 1. Copy Address to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Copy Bank to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L by 1 and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H to 1.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L by 2 and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H to 1. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H &amp; $80). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L by 2 and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H to 1. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L by 1 and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H to 1. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to (Operand + 1).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L by 3 and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H to 1. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to (Operand + 1). Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Bank.</t>
+    </r>
+  </si>
+  <si>
+    <t>Absolute Indexed Indirect (a,x) (Jump</t>
+  </si>
+  <si>
+    <t>BNE (D0)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Decide to branch if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>CMP (D1)</t>
+  </si>
+  <si>
+    <t>CMP (D2)</t>
+  </si>
+  <si>
+    <t>CMP (D3)</t>
+  </si>
+  <si>
+    <t>PEI (D4)</t>
+  </si>
+  <si>
+    <t>Direct Page Indirect</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L is 0, Read (((Address.L + 1) &amp; $FF) | (Address.H &lt;&lt; 8)), otherwise read Address + 1</t>
+    </r>
+  </si>
+  <si>
+    <t>CMP (D5)</t>
+  </si>
+  <si>
+    <t>DEC (D6)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform Operand.L -= 1, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off Operand.L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform Operand.L -= 1, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80), and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off Operand.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>CMP (D7)</t>
+  </si>
+  <si>
+    <t>CLD (D8)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag to 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>CMP (D9)</t>
+  </si>
+  <si>
+    <t>PHX (DA)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L onto stack.</t>
+    </r>
+  </si>
+  <si>
+    <t>STP (DB)</t>
+  </si>
+  <si>
+    <t>Stop processor.</t>
+  </si>
+  <si>
+    <t>JML (DC)</t>
+  </si>
+  <si>
+    <t>Absolute Indirect Long (Jump)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L is 0, Read (((Pointer.L + 2) &amp; $FF) | (Pointer.H &lt;&lt; 8)), otherwise read Pointer + 2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Operand. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to Bank.</t>
+    </r>
+  </si>
+  <si>
+    <t>CMP (DD)</t>
+  </si>
+  <si>
+    <t>DEC (DE)</t>
+  </si>
+  <si>
+    <t>CMP (DF)</t>
+  </si>
+  <si>
+    <t>CPX (E0)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &gt;= Operand.L), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L == Operand.L), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag based off ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L - Operand.L) &amp; $80) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>SBC (E1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  if (Lo &lt; 0) Lo -= 6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  BorrowToHi = Lo &lt; 0 ? 1 : 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  if (HiSum &lt; 0) HiSum -= 6.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  Result = ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L) - ui16(Operand) - (1 - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = Result &lt;= $FF.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = ((ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L) ^ ui16(Operand)) &amp; (ui16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L) ^ ui8(Result)) &amp; $80) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  HiSum = int16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 4) - int16(Operand &gt;&gt; 4) - BorrowToHi.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 4) ^ (Operand &gt;&gt; 4)) &amp; ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L &gt;&gt; 4) ^ HiSum) &amp; $08) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = HiSum &gt;= 0.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  Lo = int16(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; 0x0F) - int16(Operand &amp; 0x0F) - (1 - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>SEP (E2)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> |= (Operand.L &amp; ~(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag)).</t>
+    </r>
+  </si>
+  <si>
+    <t>SBC (E3)</t>
+  </si>
+  <si>
+    <t>CPX (E4)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &gt;= Operand.L), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L == Operand.L), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag based off ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L - Operand.L) &amp; $80) != 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>SBC (E5)</t>
+  </si>
+  <si>
+    <t>INC (E6)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform Operand.L += 1, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (Operand.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off Operand.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>SBC (E7)</t>
+  </si>
+  <si>
+    <t>INX (E8)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L += 1, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>.L.</t>
     </r>
   </si>
   <si>
+    <t>SBC (E9)</t>
+  </si>
+  <si>
+    <t>NOP (EA)</t>
+  </si>
+  <si>
+    <t>XBA (EB)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Swap </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>CPX (EC)</t>
+  </si>
+  <si>
+    <t>SBC (ED)</t>
+  </si>
+  <si>
+    <t>INC (EE)</t>
+  </si>
+  <si>
+    <t>SBC (EF)</t>
+  </si>
+  <si>
+    <t>BEQ (F0)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Decide to branch if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is 1.</t>
+    </r>
+  </si>
+  <si>
+    <t>SBC (F1)</t>
+  </si>
+  <si>
+    <t>SBC (F2)</t>
+  </si>
+  <si>
+    <t>SBC (F3)</t>
+  </si>
+  <si>
+    <t>PEA (F4)</t>
+  </si>
+  <si>
+    <t>Absolute (Push)</t>
+  </si>
+  <si>
+    <t>SBC (F5)</t>
+  </si>
+  <si>
+    <t>INC (F6)</t>
+  </si>
+  <si>
+    <t>SBC (F7)</t>
+  </si>
+  <si>
+    <t>SED (F8)</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Set the </t>
     </r>
@@ -11067,7 +13504,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>I</t>
+      <t>D</t>
     </r>
     <r>
       <rPr>
@@ -11081,107 +13518,61 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Set the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag to 0.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag to 1.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag to 0.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set Operand.L to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> with </t>
+    <t>SBC (F9)</t>
+  </si>
+  <si>
+    <t>PLX (FA)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L by 1 and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.H to 1. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Set </t>
     </r>
     <r>
       <rPr>
@@ -11202,6 +13593,119 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve">.L to Operand.L, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L &amp; $80), and set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L.</t>
+    </r>
+  </si>
+  <si>
+    <t>XCE (FB)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Exchanges the Carry and Emulation flags. If Emulation mode is entered, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve"> and </t>
     </r>
     <r>
@@ -11213,22 +13717,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flags set.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flags are set to 1, </t>
     </r>
     <r>
       <rPr>
@@ -11249,7 +13748,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">.L to </t>
+      <t xml:space="preserve">.H is set to 1, and </t>
     </r>
     <r>
       <rPr>
@@ -11270,7 +13769,91 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">.L and </t>
+      <t xml:space="preserve">.H and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H are cleared to 0.</t>
+    </r>
+  </si>
+  <si>
+    <t>JSR (FC)</t>
+  </si>
+  <si>
+    <t>Absolute Indexed Indirect (a,x) (Jump)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bank = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Perform Pointer += </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
     </r>
     <r>
       <rPr>
@@ -11291,12 +13874,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>.H to 1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
+      <t xml:space="preserve">.L by 2 and set </t>
     </r>
     <r>
       <rPr>
@@ -11317,237 +13895,50 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">.L to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.H to 1.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dec. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L by 3 and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.H to 1.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dec. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L by 1 and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.H to 1.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dec. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L by 2 and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.H to 1.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dec. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L by 2 and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H to 1. Perform </t>
+      <t xml:space="preserve">.H to 1. </t>
+    </r>
+  </si>
+  <si>
+    <t>SBC (FD)</t>
+  </si>
+  <si>
+    <t>INC (FE)</t>
+  </si>
+  <si>
+    <t>SBC (FF)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">* If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.l is not 0, read (Address + 1), otherwise read (Address &amp; $FF00) | ui8(Address.L + 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>* The Single-Step Tests require this to be “Read Address + 1,” but this is an error in the tests.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Enable writes to </t>
     </r>
     <r>
       <rPr>
@@ -11568,54 +13959,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> = Address.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dec. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L by 3 and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H to 1. Copy Address to </t>
+      <t xml:space="preserve"> (disabled by NMI/IRQ).  Copy Address to </t>
     </r>
     <r>
       <rPr>
@@ -11636,7 +13980,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">. Copy Bank to </t>
+      <t xml:space="preserve">.  Set </t>
     </r>
     <r>
       <rPr>
@@ -11657,2378 +14001,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L by 1 and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.H to 1.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L by 2 and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H to 1. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to Operand. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H &amp; $80). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L by 2 and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H to 1. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to Operand.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L by 1 and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H to 1. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to (Operand + 1).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L by 3 and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H to 1. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to (Operand + 1). Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to Bank.</t>
-    </r>
-  </si>
-  <si>
-    <t>Absolute Indexed Indirect (a,x) (Jump</t>
-  </si>
-  <si>
-    <t>BNE (D0)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Decide to branch if </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is 0.</t>
-    </r>
-  </si>
-  <si>
-    <t>CMP (D1)</t>
-  </si>
-  <si>
-    <t>CMP (D2)</t>
-  </si>
-  <si>
-    <t>CMP (D3)</t>
-  </si>
-  <si>
-    <t>PEI (D4)</t>
-  </si>
-  <si>
-    <t>Direct Page Indirect</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L is 0, Read (((Address.L + 1) &amp; $FF) | (Address.H &lt;&lt; 8)), otherwise read Address + 1</t>
-    </r>
-  </si>
-  <si>
-    <t>CMP (D5)</t>
-  </si>
-  <si>
-    <t>DEC (D6)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform Operand.L -= 1, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.L &amp; $80) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off Operand.L.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform Operand.L -= 1, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.L &amp; $80), and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off Operand.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>CMP (D7)</t>
-  </si>
-  <si>
-    <t>CLD (D8)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag to 0.</t>
-    </r>
-  </si>
-  <si>
-    <t>CMP (D9)</t>
-  </si>
-  <si>
-    <t>PHX (DA)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Push </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L onto stack.</t>
-    </r>
-  </si>
-  <si>
-    <t>STP (DB)</t>
-  </si>
-  <si>
-    <t>Stop processor.</t>
-  </si>
-  <si>
-    <t>JML (DC)</t>
-  </si>
-  <si>
-    <t>Absolute Indirect Long (Jump)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L is 0, Read (((Pointer.L + 2) &amp; $FF) | (Pointer.H &lt;&lt; 8)), otherwise read Pointer + 2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to Operand. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to Bank.</t>
-    </r>
-  </si>
-  <si>
-    <t>CMP (DD)</t>
-  </si>
-  <si>
-    <t>DEC (DE)</t>
-  </si>
-  <si>
-    <t>CMP (DF)</t>
-  </si>
-  <si>
-    <t>CPX (E0)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &gt;= Operand.L), set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L == Operand.L), and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag based off ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L - Operand.L) &amp; $80) != 0.</t>
-    </r>
-  </si>
-  <si>
-    <t>SBC (E1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  if (Lo &lt; 0) Lo -= 6.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  BorrowToHi = Lo &lt; 0 ? 1 : 0.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  if (HiSum &lt; 0) HiSum -= 6.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  Result = ui16(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L) - ui16(Operand) - (1 - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = Result &lt;= $FF.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = ((ui16(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L) ^ ui16(Operand)) &amp; (ui16(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L) ^ ui8(Result)) &amp; $80) != 0.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  HiSum = int16(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L &gt;&gt; 4) - int16(Operand &gt;&gt; 4) - BorrowToHi.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = (((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L &gt;&gt; 4) ^ (Operand &gt;&gt; 4)) &amp; ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L &gt;&gt; 4) ^ HiSum) &amp; $08) != 0.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = HiSum &gt;= 0.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">  Lo = int16(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; 0x0F) - int16(Operand &amp; 0x0F) - (1 - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>);</t>
-    </r>
-  </si>
-  <si>
-    <t>SEP (E2)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> |= (Operand.L &amp; ~(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag | </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag)).</t>
-    </r>
-  </si>
-  <si>
-    <t>SBC (E3)</t>
-  </si>
-  <si>
-    <t>CPX (E4)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &gt;= Operand.L), set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L == Operand.L), and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag based off ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L - Operand.L) &amp; $80) != 0.</t>
-    </r>
-  </si>
-  <si>
-    <t>SBC (E5)</t>
-  </si>
-  <si>
-    <t>INC (E6)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform Operand.L += 1, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (Operand.L &amp; $80), set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off Operand.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>SBC (E7)</t>
-  </si>
-  <si>
-    <t>INX (E8)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L += 1, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80), set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>SBC (E9)</t>
-  </si>
-  <si>
-    <t>NOP (EA)</t>
-  </si>
-  <si>
-    <t>XBA (EB)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Swap </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80), and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>CPX (EC)</t>
-  </si>
-  <si>
-    <t>SBC (ED)</t>
-  </si>
-  <si>
-    <t>INC (EE)</t>
-  </si>
-  <si>
-    <t>SBC (EF)</t>
-  </si>
-  <si>
-    <t>BEQ (F0)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Decide to branch if </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is 1.</t>
-    </r>
-  </si>
-  <si>
-    <t>SBC (F1)</t>
-  </si>
-  <si>
-    <t>SBC (F2)</t>
-  </si>
-  <si>
-    <t>SBC (F3)</t>
-  </si>
-  <si>
-    <t>PEA (F4)</t>
-  </si>
-  <si>
-    <t>Absolute (Push)</t>
-  </si>
-  <si>
-    <t>SBC (F5)</t>
-  </si>
-  <si>
-    <t>INC (F6)</t>
-  </si>
-  <si>
-    <t>SBC (F7)</t>
-  </si>
-  <si>
-    <t>SED (F8)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Set the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag to 1.</t>
-    </r>
-  </si>
-  <si>
-    <t>SBC (F9)</t>
-  </si>
-  <si>
-    <t>PLX (FA)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L by 1 and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H to 1. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L to Operand.L, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L &amp; $80), and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based off </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L.</t>
-    </r>
-  </si>
-  <si>
-    <t>XCE (FB)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Exchanges the Carry and Emulation flags. If Emulation mode is entered, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flags are set to 1, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H is set to 1, and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.H are cleared to 0.</t>
-    </r>
-  </si>
-  <si>
-    <t>JSR (FC)</t>
-  </si>
-  <si>
-    <t>Absolute Indexed Indirect (a,x) (Jump)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Bank = </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Perform Pointer += </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dec. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.L by 2 and set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.H to 1. </t>
-    </r>
-  </si>
-  <si>
-    <t>SBC (FD)</t>
-  </si>
-  <si>
-    <t>INC (FE)</t>
-  </si>
-  <si>
-    <t>SBC (FF)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">* If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.l is not 0, read (Address + 1), otherwise read (Address &amp; $FF00) | ui8(Address.L + 1)</t>
-    </r>
-  </si>
-  <si>
-    <t>* The Single-Step Tests require this to be “Read Address + 1,” but this is an error in the tests.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Enable writes to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (disabled by NMI/IRQ).  Copy Address to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.  Set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> to 0.</t>
     </r>
+  </si>
+  <si>
+    <t>Set Operand to A.</t>
   </si>
 </sst>
 </file>
@@ -14206,7 +14183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -14288,8 +14265,8 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -14300,15 +14277,14 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -14798,7 +14774,7 @@
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14838,7 +14814,7 @@
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="14" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14860,40 +14836,40 @@
       <c r="C22" s="21"/>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="39" t="s">
+      <c r="A24" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="39"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
+      <c r="A25" s="40"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="39"/>
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
+      <c r="A26" s="40"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="39"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
+      <c r="A27" s="40"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="40" t="s">
+      <c r="A28" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="40"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="39" t="s">
+      <c r="A29" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
@@ -15033,7 +15009,7 @@
         <v>5.2</v>
       </c>
       <c r="B75" s="38" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C75" s="14" t="s">
         <v>37</v>
@@ -15096,7 +15072,7 @@
     </row>
     <row r="83" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15223,7 +15199,7 @@
       </c>
       <c r="B131" s="9"/>
       <c r="C131" s="14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15284,40 +15260,40 @@
       <c r="B137" s="20"/>
       <c r="C137" s="22"/>
     </row>
-    <row r="139" spans="1:3" s="41" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="42"/>
-      <c r="B139" s="42"/>
-      <c r="C139" s="42"/>
-    </row>
-    <row r="140" spans="1:3" s="41" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="42"/>
-      <c r="B140" s="42"/>
-      <c r="C140" s="42"/>
-    </row>
-    <row r="141" spans="1:3" s="41" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="42"/>
-      <c r="B141" s="42"/>
-      <c r="C141" s="42"/>
-    </row>
-    <row r="142" spans="1:3" s="41" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="42"/>
-      <c r="B142" s="42"/>
-      <c r="C142" s="42"/>
-    </row>
-    <row r="143" spans="1:3" s="41" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="42"/>
-      <c r="B143" s="42"/>
-      <c r="C143" s="42"/>
-    </row>
-    <row r="144" spans="1:3" s="41" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="42"/>
-      <c r="B144" s="42"/>
-      <c r="C144" s="42"/>
+    <row r="139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="35"/>
+      <c r="B139" s="35"/>
+      <c r="C139" s="35"/>
+    </row>
+    <row r="140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="35"/>
+      <c r="B140" s="35"/>
+      <c r="C140" s="35"/>
+    </row>
+    <row r="141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="35"/>
+      <c r="B141" s="35"/>
+      <c r="C141" s="35"/>
+    </row>
+    <row r="142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="35"/>
+      <c r="B142" s="35"/>
+      <c r="C142" s="35"/>
+    </row>
+    <row r="143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="35"/>
+      <c r="B143" s="35"/>
+      <c r="C143" s="35"/>
+    </row>
+    <row r="144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="35"/>
+      <c r="B144" s="35"/>
+      <c r="C144" s="35"/>
     </row>
     <row r="145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="39"/>
-      <c r="B145" s="39"/>
-      <c r="C145" s="39"/>
+      <c r="A145" s="40"/>
+      <c r="B145" s="40"/>
+      <c r="C145" s="40"/>
     </row>
     <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
@@ -15841,14 +15817,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B367" s="9"/>
-      <c r="C367" s="35" t="s">
+      <c r="C367" s="39" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="8"/>
       <c r="B368" s="9"/>
-      <c r="C368" s="35"/>
+      <c r="C368" s="39"/>
     </row>
     <row r="369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="18">
@@ -16125,7 +16101,7 @@
       </c>
       <c r="B479" s="9"/>
       <c r="C479" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16145,7 +16121,7 @@
       </c>
       <c r="B481" s="9"/>
       <c r="C481" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16870,14 +16846,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B839" s="9"/>
-      <c r="C839" s="35" t="s">
+      <c r="C839" s="39" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="8"/>
       <c r="B840" s="9"/>
-      <c r="C840" s="35"/>
+      <c r="C840" s="39"/>
     </row>
     <row r="841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="18">
@@ -17118,14 +17094,14 @@
       <c r="B950" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C950" s="35" t="s">
+      <c r="C950" s="39" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="8"/>
       <c r="B951" s="9"/>
-      <c r="C951" s="35"/>
+      <c r="C951" s="39"/>
     </row>
     <row r="952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="8">
@@ -17977,14 +17953,14 @@
         <v>3.1</v>
       </c>
       <c r="B1248" s="9"/>
-      <c r="C1248" s="35" t="s">
+      <c r="C1248" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="1249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1249" s="8"/>
       <c r="B1249" s="9"/>
-      <c r="C1249" s="35"/>
+      <c r="C1249" s="39"/>
     </row>
     <row r="1250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1250" s="15">
@@ -18119,14 +18095,14 @@
         <v>3.1</v>
       </c>
       <c r="B1307" s="9"/>
-      <c r="C1307" s="35" t="s">
+      <c r="C1307" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="1308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1308" s="8"/>
       <c r="B1308" s="9"/>
-      <c r="C1308" s="35"/>
+      <c r="C1308" s="39"/>
     </row>
     <row r="1309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1309" s="15">
@@ -18176,14 +18152,14 @@
         <v>6.1</v>
       </c>
       <c r="B1314" s="9"/>
-      <c r="C1314" s="35" t="s">
+      <c r="C1314" s="39" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="1315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1315" s="8"/>
       <c r="B1315" s="9"/>
-      <c r="C1315" s="35"/>
+      <c r="C1315" s="39"/>
     </row>
     <row r="1316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1316" s="18">
@@ -18500,7 +18476,7 @@
       </c>
       <c r="B1423" s="9"/>
       <c r="C1423" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="1424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18843,7 +18819,7 @@
       </c>
       <c r="B1600" s="9"/>
       <c r="C1600" s="10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1601" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19347,14 +19323,14 @@
         <v>6.1</v>
       </c>
       <c r="B1787" s="9"/>
-      <c r="C1787" s="35" t="s">
+      <c r="C1787" s="39" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="1788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1788" s="8"/>
       <c r="B1788" s="9"/>
-      <c r="C1788" s="35"/>
+      <c r="C1788" s="39"/>
     </row>
     <row r="1789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1789" s="18">
@@ -19697,7 +19673,7 @@
       </c>
       <c r="B1903" s="9"/>
       <c r="C1903" s="10" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19856,7 +19832,7 @@
         <v>5.2</v>
       </c>
       <c r="B1963" s="38" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C1963" s="14" t="s">
         <v>37</v>
@@ -19919,7 +19895,7 @@
     </row>
     <row r="1971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1971" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="2007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20100,7 +20076,7 @@
       </c>
       <c r="B2025" s="9"/>
       <c r="C2025" s="10" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20607,14 +20583,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2255" s="9"/>
-      <c r="C2255" s="35" t="s">
+      <c r="C2255" s="39" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="2256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2256" s="8"/>
       <c r="B2256" s="9"/>
-      <c r="C2256" s="35"/>
+      <c r="C2256" s="39"/>
     </row>
     <row r="2257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2257" s="18">
@@ -20905,7 +20881,7 @@
       </c>
       <c r="B2369" s="9"/>
       <c r="C2369" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21232,7 +21208,7 @@
       </c>
       <c r="B2550" s="9"/>
       <c r="C2550" s="10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21630,14 +21606,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2727" s="9"/>
-      <c r="C2727" s="35" t="s">
+      <c r="C2727" s="39" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="2728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2728" s="8"/>
       <c r="B2728" s="9"/>
-      <c r="C2728" s="35"/>
+      <c r="C2728" s="39"/>
     </row>
     <row r="2729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2729" s="18">
@@ -21878,14 +21854,14 @@
       <c r="B2838" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C2838" s="35" t="s">
+      <c r="C2838" s="39" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="2839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2839" s="8"/>
       <c r="B2839" s="9"/>
-      <c r="C2839" s="35"/>
+      <c r="C2839" s="39"/>
     </row>
     <row r="2840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2840" s="8">
@@ -22578,14 +22554,14 @@
         <v>3.1</v>
       </c>
       <c r="B3077" s="9"/>
-      <c r="C3077" s="35" t="s">
+      <c r="C3077" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="3078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3078" s="8"/>
       <c r="B3078" s="9"/>
-      <c r="C3078" s="35"/>
+      <c r="C3078" s="39"/>
     </row>
     <row r="3079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3079" s="15">
@@ -22730,14 +22706,14 @@
         <v>3.1</v>
       </c>
       <c r="B3136" s="9"/>
-      <c r="C3136" s="35" t="s">
+      <c r="C3136" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="3137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3137" s="8"/>
       <c r="B3137" s="9"/>
-      <c r="C3137" s="35"/>
+      <c r="C3137" s="39"/>
     </row>
     <row r="3138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3138" s="15">
@@ -22872,14 +22848,14 @@
         <v>3.1</v>
       </c>
       <c r="B3195" s="9"/>
-      <c r="C3195" s="35" t="s">
+      <c r="C3195" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="3196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3196" s="8"/>
       <c r="B3196" s="9"/>
-      <c r="C3196" s="35"/>
+      <c r="C3196" s="39"/>
     </row>
     <row r="3197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3197" s="15">
@@ -22929,14 +22905,14 @@
         <v>6.1</v>
       </c>
       <c r="B3202" s="9"/>
-      <c r="C3202" s="35" t="s">
+      <c r="C3202" s="39" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="3203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3203" s="8"/>
       <c r="B3203" s="9"/>
-      <c r="C3203" s="35"/>
+      <c r="C3203" s="39"/>
     </row>
     <row r="3204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3204" s="18">
@@ -23263,7 +23239,7 @@
       </c>
       <c r="B3311" s="9"/>
       <c r="C3311" s="10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24116,14 +24092,14 @@
         <v>6.1</v>
       </c>
       <c r="B3675" s="9"/>
-      <c r="C3675" s="35" t="s">
+      <c r="C3675" s="39" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="3676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3676" s="8"/>
       <c r="B3676" s="9"/>
-      <c r="C3676" s="35"/>
+      <c r="C3676" s="39"/>
     </row>
     <row r="3677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3677" s="18">
@@ -24398,7 +24374,7 @@
       </c>
       <c r="B3785" s="9"/>
       <c r="C3785" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3786" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24456,7 +24432,7 @@
       </c>
       <c r="B3791" s="9"/>
       <c r="C3791" s="14" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="3792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24615,7 +24591,7 @@
         <v>5.2</v>
       </c>
       <c r="B3851" s="38" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C3851" s="14" t="s">
         <v>37</v>
@@ -24678,7 +24654,7 @@
     </row>
     <row r="3859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3859" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="3895" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25012,14 +24988,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4025" s="9"/>
-      <c r="C4025" s="35" t="s">
+      <c r="C4025" s="39" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="4026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4026" s="8"/>
       <c r="B4026" s="9"/>
-      <c r="C4026" s="35"/>
+      <c r="C4026" s="39"/>
     </row>
     <row r="4027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4027" s="8">
@@ -25309,14 +25285,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4143" s="9"/>
-      <c r="C4143" s="35" t="s">
+      <c r="C4143" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="4144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4144" s="8"/>
       <c r="B4144" s="9"/>
-      <c r="C4144" s="35"/>
+      <c r="C4144" s="39"/>
     </row>
     <row r="4145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4145" s="18">
@@ -25611,7 +25587,7 @@
       </c>
       <c r="B4257" s="9"/>
       <c r="C4257" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25886,7 +25862,7 @@
       </c>
       <c r="B4434" s="9"/>
       <c r="C4434" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26264,14 +26240,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4615" s="9"/>
-      <c r="C4615" s="35" t="s">
+      <c r="C4615" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="4616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4616" s="8"/>
       <c r="B4616" s="9"/>
-      <c r="C4616" s="35"/>
+      <c r="C4616" s="39"/>
     </row>
     <row r="4617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4617" s="18">
@@ -26512,14 +26488,14 @@
       <c r="B4726" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C4726" s="35" t="s">
+      <c r="C4726" s="39" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="4727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4727" s="8"/>
       <c r="B4727" s="9"/>
-      <c r="C4727" s="35"/>
+      <c r="C4727" s="39"/>
     </row>
     <row r="4728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4728" s="8">
@@ -27247,14 +27223,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4969" s="9"/>
-      <c r="C4969" s="35" t="s">
+      <c r="C4969" s="39" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="4970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4970" s="8"/>
       <c r="B4970" s="9"/>
-      <c r="C4970" s="35"/>
+      <c r="C4970" s="39"/>
     </row>
     <row r="4971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4971" s="8">
@@ -27383,14 +27359,14 @@
         <v>3.1</v>
       </c>
       <c r="B5024" s="9"/>
-      <c r="C5024" s="35" t="s">
+      <c r="C5024" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="5025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5025" s="8"/>
       <c r="B5025" s="9"/>
-      <c r="C5025" s="35"/>
+      <c r="C5025" s="39"/>
     </row>
     <row r="5026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5026" s="15">
@@ -27525,14 +27501,14 @@
         <v>3.1</v>
       </c>
       <c r="B5083" s="9"/>
-      <c r="C5083" s="35" t="s">
+      <c r="C5083" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="5084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5084" s="8"/>
       <c r="B5084" s="9"/>
-      <c r="C5084" s="35"/>
+      <c r="C5084" s="39"/>
     </row>
     <row r="5085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5085" s="15">
@@ -27582,14 +27558,14 @@
         <v>6.1</v>
       </c>
       <c r="B5090" s="9"/>
-      <c r="C5090" s="35" t="s">
+      <c r="C5090" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="5091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5091" s="8"/>
       <c r="B5091" s="9"/>
-      <c r="C5091" s="35"/>
+      <c r="C5091" s="39"/>
     </row>
     <row r="5092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5092" s="18">
@@ -27906,7 +27882,7 @@
       </c>
       <c r="B5199" s="9"/>
       <c r="C5199" s="10" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28176,7 +28152,7 @@
       </c>
       <c r="B5319" s="9"/>
       <c r="C5319" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28724,14 +28700,14 @@
         <v>6.1</v>
       </c>
       <c r="B5563" s="9"/>
-      <c r="C5563" s="35" t="s">
+      <c r="C5563" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="5564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5564" s="8"/>
       <c r="B5564" s="9"/>
-      <c r="C5564" s="35"/>
+      <c r="C5564" s="39"/>
     </row>
     <row r="5565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5565" s="18">
@@ -29006,7 +28982,7 @@
       </c>
       <c r="B5673" s="9"/>
       <c r="C5673" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5674" spans="1:3" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29058,7 +29034,7 @@
       </c>
       <c r="B5679" s="9"/>
       <c r="C5679" s="10" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="5680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29217,7 +29193,7 @@
         <v>5.2</v>
       </c>
       <c r="B5739" s="38" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C5739" s="10" t="s">
         <v>37</v>
@@ -29378,7 +29354,7 @@
     </row>
     <row r="5761" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5761" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="5783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29519,7 +29495,7 @@
       </c>
       <c r="B5797" s="9"/>
       <c r="C5797" s="14" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30220,14 +30196,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6031" s="9"/>
-      <c r="C6031" s="35" t="s">
+      <c r="C6031" s="39" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="6032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6032" s="8"/>
       <c r="B6032" s="9"/>
-      <c r="C6032" s="35"/>
+      <c r="C6032" s="39"/>
     </row>
     <row r="6033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6033" s="18">
@@ -30616,7 +30592,7 @@
       </c>
       <c r="B6145" s="9"/>
       <c r="C6145" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31059,7 +31035,7 @@
       </c>
       <c r="B6328" s="9"/>
       <c r="C6328" s="10" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="6329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31573,14 +31549,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6503" s="9"/>
-      <c r="C6503" s="35" t="s">
+      <c r="C6503" s="39" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="6504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6504" s="8"/>
       <c r="B6504" s="9"/>
-      <c r="C6504" s="35"/>
+      <c r="C6504" s="39"/>
     </row>
     <row r="6505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6505" s="18">
@@ -31919,14 +31895,14 @@
       <c r="B6614" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C6614" s="35" t="s">
+      <c r="C6614" s="39" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="6615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6615" s="8"/>
       <c r="B6615" s="9"/>
-      <c r="C6615" s="35"/>
+      <c r="C6615" s="39"/>
     </row>
     <row r="6616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6616" s="8">
@@ -32913,14 +32889,14 @@
         <v>3.1</v>
       </c>
       <c r="B6853" s="9"/>
-      <c r="C6853" s="35" t="s">
+      <c r="C6853" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="6854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6854" s="8"/>
       <c r="B6854" s="9"/>
-      <c r="C6854" s="35"/>
+      <c r="C6854" s="39"/>
     </row>
     <row r="6855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6855" s="8">
@@ -33053,14 +33029,14 @@
         <v>3.1</v>
       </c>
       <c r="B6912" s="9"/>
-      <c r="C6912" s="35" t="s">
+      <c r="C6912" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="6913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6913" s="8"/>
       <c r="B6913" s="9"/>
-      <c r="C6913" s="35"/>
+      <c r="C6913" s="39"/>
     </row>
     <row r="6914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6914" s="8">
@@ -33293,14 +33269,14 @@
         <v>3.1</v>
       </c>
       <c r="B6971" s="9"/>
-      <c r="C6971" s="35" t="s">
+      <c r="C6971" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="6972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6972" s="8"/>
       <c r="B6972" s="9"/>
-      <c r="C6972" s="35"/>
+      <c r="C6972" s="39"/>
     </row>
     <row r="6973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6973" s="8">
@@ -33350,14 +33326,14 @@
         <v>6.1</v>
       </c>
       <c r="B6978" s="9"/>
-      <c r="C6978" s="35" t="s">
+      <c r="C6978" s="39" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="6979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6979" s="8"/>
       <c r="B6979" s="9"/>
-      <c r="C6979" s="35"/>
+      <c r="C6979" s="39"/>
     </row>
     <row r="6980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6980" s="18">
@@ -33772,7 +33748,7 @@
       </c>
       <c r="B7087" s="9"/>
       <c r="C7087" s="10" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34136,7 +34112,7 @@
       </c>
       <c r="B7207" s="9"/>
       <c r="C7207" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="7208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34288,7 +34264,7 @@
     <row r="7318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7318" s="4"/>
       <c r="B7318" s="36" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C7318" s="37"/>
     </row>
@@ -34851,14 +34827,14 @@
         <v>6.1</v>
       </c>
       <c r="B7451" s="27"/>
-      <c r="C7451" s="35" t="s">
+      <c r="C7451" s="39" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="7452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7452" s="8"/>
       <c r="B7452" s="27"/>
-      <c r="C7452" s="35"/>
+      <c r="C7452" s="39"/>
     </row>
     <row r="7453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7453" s="18">
@@ -35211,14 +35187,14 @@
       <c r="B7558" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C7558" s="35" t="s">
+      <c r="C7558" s="39" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="7559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7559" s="18"/>
       <c r="B7559" s="9"/>
-      <c r="C7559" s="35"/>
+      <c r="C7559" s="39"/>
     </row>
     <row r="7560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7560" s="8">
@@ -35418,57 +35394,72 @@
       <c r="A7627" s="8">
         <v>5.2</v>
       </c>
-      <c r="B7627" s="9" t="s">
-        <v>44</v>
+      <c r="B7627" s="38" t="s">
+        <v>584</v>
       </c>
       <c r="C7627" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7628" s="8">
-        <v>6.1</v>
-      </c>
-      <c r="B7628" s="9"/>
-      <c r="C7628" s="10" t="s">
-        <v>481</v>
-      </c>
+      <c r="A7628" s="8"/>
+      <c r="B7628" s="38"/>
+      <c r="C7628" s="10"/>
     </row>
     <row r="7629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7629" s="18">
-        <v>6.2</v>
-      </c>
-      <c r="B7629" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="C7629" s="10" t="s">
-        <v>47</v>
-      </c>
+      <c r="A7629" s="8"/>
+      <c r="B7629" s="38"/>
+      <c r="C7629" s="10"/>
     </row>
     <row r="7630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7630" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="B7630" s="9"/>
+      <c r="C7630" s="10" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="7631" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7631" s="18">
+        <v>6.2</v>
+      </c>
+      <c r="B7631" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C7631" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7632" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7632" s="8">
         <v>7.1</v>
       </c>
-      <c r="B7630" s="9"/>
-      <c r="C7630" s="10"/>
-    </row>
-    <row r="7631" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7631" s="8">
+      <c r="B7632" s="9"/>
+      <c r="C7632" s="10"/>
+    </row>
+    <row r="7633" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7633" s="8">
         <v>7.2</v>
       </c>
-      <c r="B7631" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7631" s="10" t="s">
+      <c r="B7633" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7633" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7632" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7632" s="19" t="s">
+    <row r="7634" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7634" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B7632" s="20"/>
-      <c r="C7632" s="22"/>
+      <c r="B7634" s="20"/>
+      <c r="C7634" s="22"/>
+    </row>
+    <row r="7635" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7635" t="s">
+        <v>585</v>
+      </c>
     </row>
     <row r="7671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7671" s="1" t="s">
@@ -36595,7 +36586,7 @@
       </c>
       <c r="B8210" s="9"/>
       <c r="C8210" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -37192,14 +37183,14 @@
       <c r="B8502" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C8502" s="35" t="s">
+      <c r="C8502" s="39" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="8503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8503" s="8"/>
       <c r="B8503" s="9"/>
-      <c r="C8503" s="35"/>
+      <c r="C8503" s="39"/>
     </row>
     <row r="8504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8504" s="8">
@@ -37878,14 +37869,14 @@
         <v>3.1</v>
       </c>
       <c r="B8741" s="9"/>
-      <c r="C8741" s="35" t="s">
+      <c r="C8741" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="8742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8742" s="8"/>
       <c r="B8742" s="9"/>
-      <c r="C8742" s="35"/>
+      <c r="C8742" s="39"/>
     </row>
     <row r="8743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8743" s="15">
@@ -38018,14 +38009,14 @@
         <v>3.1</v>
       </c>
       <c r="B8800" s="9"/>
-      <c r="C8800" s="35" t="s">
+      <c r="C8800" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="8801" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8801" s="8"/>
       <c r="B8801" s="9"/>
-      <c r="C8801" s="35"/>
+      <c r="C8801" s="39"/>
     </row>
     <row r="8802" spans="1:3" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8802" s="15">
@@ -38158,14 +38149,14 @@
         <v>3.1</v>
       </c>
       <c r="B8859" s="9"/>
-      <c r="C8859" s="35" t="s">
+      <c r="C8859" s="39" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="8860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8860" s="8"/>
       <c r="B8860" s="9"/>
-      <c r="C8860" s="35"/>
+      <c r="C8860" s="39"/>
     </row>
     <row r="8861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8861" s="15">
@@ -38736,7 +38727,7 @@
       </c>
       <c r="B9093" s="9"/>
       <c r="C9093" s="10" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39663,7 +39654,7 @@
         <v>5.2</v>
       </c>
       <c r="B9515" s="38" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C9515" s="10" t="s">
         <v>37</v>
@@ -39726,7 +39717,7 @@
     </row>
     <row r="9523" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9523" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="9559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40820,7 +40811,7 @@
       </c>
       <c r="B10098" s="9"/>
       <c r="C10098" s="10" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="10099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41445,14 +41436,14 @@
       <c r="B10390" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C10390" s="35" t="s">
+      <c r="C10390" s="39" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="10391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10391" s="8"/>
       <c r="B10391" s="9"/>
-      <c r="C10391" s="35"/>
+      <c r="C10391" s="39"/>
     </row>
     <row r="10392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10392" s="8">
@@ -42145,14 +42136,14 @@
         <v>3.1</v>
       </c>
       <c r="B10629" s="9"/>
-      <c r="C10629" s="35" t="s">
+      <c r="C10629" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="10630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10630" s="8"/>
       <c r="B10630" s="9"/>
-      <c r="C10630" s="35"/>
+      <c r="C10630" s="39"/>
     </row>
     <row r="10631" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10631" s="15">
@@ -42287,14 +42278,14 @@
         <v>3.1</v>
       </c>
       <c r="B10688" s="9"/>
-      <c r="C10688" s="35" t="s">
+      <c r="C10688" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="10689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10689" s="8"/>
       <c r="B10689" s="9"/>
-      <c r="C10689" s="35"/>
+      <c r="C10689" s="39"/>
     </row>
     <row r="10690" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10690" s="15">
@@ -42429,14 +42420,14 @@
         <v>3.1</v>
       </c>
       <c r="B10747" s="9"/>
-      <c r="C10747" s="35" t="s">
+      <c r="C10747" s="39" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="10748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10748" s="8"/>
       <c r="B10748" s="9"/>
-      <c r="C10748" s="35"/>
+      <c r="C10748" s="39"/>
     </row>
     <row r="10749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10749" s="15">
@@ -43866,14 +43857,14 @@
         <v>2.1</v>
       </c>
       <c r="B11335" s="9"/>
-      <c r="C11335" s="35" t="s">
+      <c r="C11335" s="39" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="11336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11336" s="8"/>
       <c r="B11336" s="9"/>
-      <c r="C11336" s="35"/>
+      <c r="C11336" s="39"/>
     </row>
     <row r="11337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11337" s="8">
@@ -44031,7 +44022,7 @@
         <v>5.2</v>
       </c>
       <c r="B11403" s="38" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C11403" s="10" t="s">
         <v>37</v>
@@ -44070,14 +44061,14 @@
         <v>7.1</v>
       </c>
       <c r="B11408" s="9"/>
-      <c r="C11408" s="35" t="s">
+      <c r="C11408" s="39" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="11409" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11409" s="8"/>
       <c r="B11409" s="9"/>
-      <c r="C11409" s="35"/>
+      <c r="C11409" s="39"/>
     </row>
     <row r="11410" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11410" s="8">
@@ -44099,7 +44090,7 @@
     </row>
     <row r="11412" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11412" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44304,14 +44295,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B11516" s="9"/>
-      <c r="C11516" s="35" t="s">
+      <c r="C11516" s="39" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="11517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11517" s="8"/>
       <c r="B11517" s="9"/>
-      <c r="C11517" s="35"/>
+      <c r="C11517" s="39"/>
     </row>
     <row r="11518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11518" s="8">
@@ -44432,14 +44423,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B11575" s="9"/>
-      <c r="C11575" s="35" t="s">
+      <c r="C11575" s="39" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="11576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11576" s="8"/>
       <c r="B11576" s="9"/>
-      <c r="C11576" s="35"/>
+      <c r="C11576" s="39"/>
     </row>
     <row r="11577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11577" s="8">
@@ -44560,14 +44551,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B11634" s="9"/>
-      <c r="C11634" s="35" t="s">
+      <c r="C11634" s="39" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="11635" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11635" s="8"/>
       <c r="B11635" s="9"/>
-      <c r="C11635" s="35"/>
+      <c r="C11635" s="39"/>
     </row>
     <row r="11636" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11636" s="8">
@@ -44707,7 +44698,7 @@
       </c>
       <c r="B11695" s="9"/>
       <c r="C11695" s="10" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="11696" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44901,14 +44892,14 @@
         <v>7.1</v>
       </c>
       <c r="B11758" s="9"/>
-      <c r="C11758" s="35" t="s">
+      <c r="C11758" s="39" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="11759" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11759" s="8"/>
       <c r="B11759" s="9"/>
-      <c r="C11759" s="35"/>
+      <c r="C11759" s="39"/>
     </row>
     <row r="11760" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11760" s="8">
@@ -45080,14 +45071,14 @@
         <v>2.1</v>
       </c>
       <c r="B11866" s="9"/>
-      <c r="C11866" s="35" t="s">
+      <c r="C11866" s="39" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="11867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11867" s="8"/>
       <c r="B11867" s="9"/>
-      <c r="C11867" s="35"/>
+      <c r="C11867" s="39"/>
     </row>
     <row r="11868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11868" s="8">
@@ -45389,14 +45380,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B12047" s="9"/>
-      <c r="C12047" s="35" t="s">
+      <c r="C12047" s="39" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="12048" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12048" s="8"/>
       <c r="B12048" s="9"/>
-      <c r="C12048" s="35"/>
+      <c r="C12048" s="39"/>
     </row>
     <row r="12049" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12049" s="8">
@@ -45521,14 +45512,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B12106" s="9"/>
-      <c r="C12106" s="35" t="s">
+      <c r="C12106" s="39" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12107" s="8"/>
       <c r="B12107" s="9"/>
-      <c r="C12107" s="35"/>
+      <c r="C12107" s="39"/>
     </row>
     <row r="12108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12108" s="8">
@@ -45672,7 +45663,7 @@
       </c>
       <c r="B12167" s="9"/>
       <c r="C12167" s="10" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="12168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45836,14 +45827,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12226" s="9"/>
-      <c r="C12226" s="35" t="s">
+      <c r="C12226" s="39" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12227" s="8"/>
       <c r="B12227" s="9"/>
-      <c r="C12227" s="35"/>
+      <c r="C12227" s="39"/>
     </row>
     <row r="12228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12228" s="8">
@@ -45865,7 +45856,7 @@
     </row>
     <row r="12273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12273" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B12273" s="2" t="s">
         <v>22</v>
@@ -45909,7 +45900,7 @@
       </c>
       <c r="B12277" s="9"/>
       <c r="C12277" s="10" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45919,14 +45910,14 @@
       <c r="B12278" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C12278" s="35" t="s">
+      <c r="C12278" s="39" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="12279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12279" s="8"/>
       <c r="B12279" s="9"/>
-      <c r="C12279" s="35"/>
+      <c r="C12279" s="39"/>
     </row>
     <row r="12280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12280" s="8">
@@ -45991,7 +45982,7 @@
     </row>
     <row r="12332" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12332" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B12332" s="2" t="s">
         <v>19</v>
@@ -46170,14 +46161,14 @@
         <v>7.1</v>
       </c>
       <c r="B12352" s="9"/>
-      <c r="C12352" s="35" t="s">
+      <c r="C12352" s="39" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12353" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12353" s="8"/>
       <c r="B12353" s="9"/>
-      <c r="C12353" s="35"/>
+      <c r="C12353" s="39"/>
     </row>
     <row r="12354" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12354" s="8">
@@ -46199,7 +46190,7 @@
     </row>
     <row r="12391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12391" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B12391" s="2" t="s">
         <v>19</v>
@@ -46334,14 +46325,14 @@
         <v>6.1</v>
       </c>
       <c r="B12405" s="9"/>
-      <c r="C12405" s="35" t="s">
+      <c r="C12405" s="39" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12406" s="8"/>
       <c r="B12406" s="9"/>
-      <c r="C12406" s="35"/>
+      <c r="C12406" s="39"/>
     </row>
     <row r="12407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12407" s="8">
@@ -46363,7 +46354,7 @@
     </row>
     <row r="12450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12450" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B12450" s="2" t="s">
         <v>98</v>
@@ -46526,14 +46517,14 @@
         <v>7.1</v>
       </c>
       <c r="B12468" s="9"/>
-      <c r="C12468" s="35" t="s">
+      <c r="C12468" s="39" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12469" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12469" s="8"/>
       <c r="B12469" s="9"/>
-      <c r="C12469" s="35"/>
+      <c r="C12469" s="39"/>
     </row>
     <row r="12470" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12470" s="8">
@@ -46555,7 +46546,7 @@
     </row>
     <row r="12509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12509" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B12509" s="2" t="s">
         <v>6</v>
@@ -46567,7 +46558,7 @@
     <row r="12510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12510" s="4"/>
       <c r="B12510" s="36" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C12510" s="37"/>
     </row>
@@ -46661,7 +46652,7 @@
         <v>4.2</v>
       </c>
       <c r="B12520" s="38" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C12520" s="10" t="s">
         <v>69</v>
@@ -46719,7 +46710,7 @@
       </c>
       <c r="B12527" s="9"/>
       <c r="C12527" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="12528" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46742,7 +46733,7 @@
     </row>
     <row r="12568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12568" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B12568" s="2" t="s">
         <v>24</v>
@@ -46821,14 +46812,14 @@
         <v>3.1</v>
       </c>
       <c r="B12576" s="9"/>
-      <c r="C12576" s="35" t="s">
+      <c r="C12576" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="12577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12577" s="8"/>
       <c r="B12577" s="9"/>
-      <c r="C12577" s="35"/>
+      <c r="C12577" s="39"/>
     </row>
     <row r="12578" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12578" s="8">
@@ -46860,14 +46851,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12581" s="27"/>
-      <c r="C12581" s="35" t="s">
+      <c r="C12581" s="39" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12582" s="8"/>
       <c r="B12582" s="27"/>
-      <c r="C12582" s="35"/>
+      <c r="C12582" s="39"/>
     </row>
     <row r="12583" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12583" s="8">
@@ -46889,7 +46880,7 @@
     </row>
     <row r="12627" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12627" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B12627" s="2" t="s">
         <v>6</v>
@@ -46968,14 +46959,14 @@
         <v>3.1</v>
       </c>
       <c r="B12635" s="9"/>
-      <c r="C12635" s="35" t="s">
+      <c r="C12635" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="12636" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12636" s="8"/>
       <c r="B12636" s="9"/>
-      <c r="C12636" s="35"/>
+      <c r="C12636" s="39"/>
     </row>
     <row r="12637" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12637" s="8">
@@ -47026,7 +47017,7 @@
       </c>
       <c r="B12642" s="9"/>
       <c r="C12642" s="10" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12643" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47067,7 +47058,7 @@
     </row>
     <row r="12686" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12686" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B12686" s="2" t="s">
         <v>6</v>
@@ -47256,14 +47247,14 @@
         <v>7.1</v>
       </c>
       <c r="B12708" s="9"/>
-      <c r="C12708" s="35" t="s">
+      <c r="C12708" s="39" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12709" s="8"/>
       <c r="B12709" s="9"/>
-      <c r="C12709" s="35"/>
+      <c r="C12709" s="39"/>
     </row>
     <row r="12710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12710" s="8">
@@ -47285,7 +47276,7 @@
     </row>
     <row r="12745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12745" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B12745" s="2" t="s">
         <v>22</v>
@@ -47349,7 +47340,7 @@
       </c>
       <c r="B12751" s="9"/>
       <c r="C12751" s="10" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="12752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47372,7 +47363,7 @@
     </row>
     <row r="12804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12804" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B12804" s="2" t="s">
         <v>24</v>
@@ -47517,14 +47508,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12820" s="27"/>
-      <c r="C12820" s="35" t="s">
+      <c r="C12820" s="39" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12821" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12821" s="8"/>
       <c r="B12821" s="27"/>
-      <c r="C12821" s="35"/>
+      <c r="C12821" s="39"/>
     </row>
     <row r="12822" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12822" s="8">
@@ -47546,7 +47537,7 @@
     </row>
     <row r="12863" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12863" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B12863" s="2" t="s">
         <v>15</v>
@@ -47615,7 +47606,7 @@
         <v>219</v>
       </c>
       <c r="C12870" s="10" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="12871" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47624,7 +47615,7 @@
       </c>
       <c r="B12871" s="9"/>
       <c r="C12871" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12872" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47647,7 +47638,7 @@
     </row>
     <row r="12922" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12922" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B12922" s="2" t="s">
         <v>24</v>
@@ -47735,12 +47726,12 @@
       </c>
       <c r="B12932" s="30"/>
       <c r="C12932" s="31" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12981" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B12981" s="2" t="s">
         <v>6</v>
@@ -47752,7 +47743,7 @@
     <row r="12982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12982" s="4"/>
       <c r="B12982" s="36" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C12982" s="37"/>
     </row>
@@ -47868,7 +47859,7 @@
         <v>5.2</v>
       </c>
       <c r="B12994" s="38" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C12994" s="10" t="s">
         <v>69</v>
@@ -47890,7 +47881,7 @@
       </c>
       <c r="B12997" s="9"/>
       <c r="C12997" s="10" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="12998" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47913,7 +47904,7 @@
     </row>
     <row r="13040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13040" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B13040" s="2" t="s">
         <v>24</v>
@@ -48058,14 +48049,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B13056" s="9"/>
-      <c r="C13056" s="35" t="s">
+      <c r="C13056" s="39" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="13057" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13057" s="8"/>
       <c r="B13057" s="9"/>
-      <c r="C13057" s="35"/>
+      <c r="C13057" s="39"/>
     </row>
     <row r="13058" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13058" s="8">
@@ -48087,7 +48078,7 @@
     </row>
     <row r="13099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13099" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B13099" s="2" t="s">
         <v>98</v>
@@ -48237,7 +48228,7 @@
       </c>
       <c r="B13115" s="9"/>
       <c r="C13115" s="10" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13116" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48278,7 +48269,7 @@
     </row>
     <row r="13158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13158" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B13158" s="2" t="s">
         <v>19</v>
@@ -48415,14 +48406,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B13172" s="9"/>
-      <c r="C13172" s="35" t="s">
+      <c r="C13172" s="39" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="13173" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13173" s="8"/>
       <c r="B13173" s="9"/>
-      <c r="C13173" s="35"/>
+      <c r="C13173" s="39"/>
     </row>
     <row r="13174" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13174" s="8">
@@ -48444,7 +48435,7 @@
     </row>
     <row r="13217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13217" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B13217" s="2" t="s">
         <v>22</v>
@@ -48507,14 +48498,14 @@
         <v>2.1</v>
       </c>
       <c r="B13223" s="9"/>
-      <c r="C13223" s="35" t="s">
-        <v>528</v>
+      <c r="C13223" s="39" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="13224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13224" s="8"/>
       <c r="B13224" s="9"/>
-      <c r="C13224" s="35"/>
+      <c r="C13224" s="39"/>
     </row>
     <row r="13225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13225" s="8">
@@ -48536,7 +48527,7 @@
     </row>
     <row r="13276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13276" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B13276" s="2" t="s">
         <v>6</v>
@@ -48672,7 +48663,7 @@
         <v>5.2</v>
       </c>
       <c r="B13291" s="38" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C13291" s="10" t="s">
         <v>37</v>
@@ -48719,21 +48710,21 @@
       <c r="A13297" s="8"/>
       <c r="B13297" s="9"/>
       <c r="C13297" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13298" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13298" s="8"/>
       <c r="B13298" s="9"/>
       <c r="C13298" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="13299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13299" s="8"/>
       <c r="B13299" s="9"/>
       <c r="C13299" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48754,49 +48745,49 @@
       <c r="A13302" s="8"/>
       <c r="B13302" s="9"/>
       <c r="C13302" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="13303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13303" s="8"/>
       <c r="B13303" s="9"/>
       <c r="C13303" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="13304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13304" s="8"/>
       <c r="B13304" s="9"/>
       <c r="C13304" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13305" s="8"/>
       <c r="B13305" s="9"/>
       <c r="C13305" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="13306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13306" s="8"/>
       <c r="B13306" s="9"/>
       <c r="C13306" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13307" s="8"/>
       <c r="B13307" s="9"/>
       <c r="C13307" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13308" s="8"/>
       <c r="B13308" s="9"/>
       <c r="C13308" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="13309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48833,12 +48824,12 @@
     </row>
     <row r="13313" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13313" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="13335" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13335" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B13335" s="2" t="s">
         <v>15</v>
@@ -48916,7 +48907,7 @@
       </c>
       <c r="B13343" s="9"/>
       <c r="C13343" s="10" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="13344" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48939,7 +48930,7 @@
     </row>
     <row r="13394" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13394" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B13394" s="2" t="s">
         <v>24</v>
@@ -49044,21 +49035,21 @@
       <c r="A13405" s="8"/>
       <c r="B13405" s="9"/>
       <c r="C13405" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13406" s="8"/>
       <c r="B13406" s="9"/>
       <c r="C13406" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="13407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13407" s="8"/>
       <c r="B13407" s="9"/>
       <c r="C13407" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13408" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49079,49 +49070,49 @@
       <c r="A13410" s="8"/>
       <c r="B13410" s="9"/>
       <c r="C13410" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="13411" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13411" s="8"/>
       <c r="B13411" s="9"/>
       <c r="C13411" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="13412" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13412" s="8"/>
       <c r="B13412" s="9"/>
       <c r="C13412" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13413" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13413" s="8"/>
       <c r="B13413" s="9"/>
       <c r="C13413" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="13414" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13414" s="8"/>
       <c r="B13414" s="9"/>
       <c r="C13414" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13415" s="8"/>
       <c r="B13415" s="9"/>
       <c r="C13415" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13416" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13416" s="8"/>
       <c r="B13416" s="9"/>
       <c r="C13416" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="13417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49158,7 +49149,7 @@
     </row>
     <row r="13453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13453" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B13453" s="2" t="s">
         <v>15</v>
@@ -49257,14 +49248,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B13463" s="9"/>
-      <c r="C13463" s="35" t="s">
-        <v>544</v>
+      <c r="C13463" s="39" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="13464" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13464" s="8"/>
       <c r="B13464" s="9"/>
-      <c r="C13464" s="35"/>
+      <c r="C13464" s="39"/>
     </row>
     <row r="13465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13465" s="8">
@@ -49286,7 +49277,7 @@
     </row>
     <row r="13512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13512" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B13512" s="2" t="s">
         <v>15</v>
@@ -49393,21 +49384,21 @@
       <c r="A13523" s="8"/>
       <c r="B13523" s="9"/>
       <c r="C13523" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13524" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13524" s="8"/>
       <c r="B13524" s="9"/>
       <c r="C13524" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="13525" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13525" s="8"/>
       <c r="B13525" s="9"/>
       <c r="C13525" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13526" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49428,49 +49419,49 @@
       <c r="A13528" s="8"/>
       <c r="B13528" s="9"/>
       <c r="C13528" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="13529" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13529" s="8"/>
       <c r="B13529" s="9"/>
       <c r="C13529" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="13530" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13530" s="8"/>
       <c r="B13530" s="9"/>
       <c r="C13530" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13531" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13531" s="8"/>
       <c r="B13531" s="9"/>
       <c r="C13531" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="13532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13532" s="8"/>
       <c r="B13532" s="9"/>
       <c r="C13532" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13533" s="8"/>
       <c r="B13533" s="9"/>
       <c r="C13533" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13534" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13534" s="8"/>
       <c r="B13534" s="9"/>
       <c r="C13534" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="13535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49507,7 +49498,7 @@
     </row>
     <row r="13571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13571" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B13571" s="2" t="s">
         <v>19</v>
@@ -49625,7 +49616,7 @@
       </c>
       <c r="B13583" s="9"/>
       <c r="C13583" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="13584" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49666,7 +49657,7 @@
     </row>
     <row r="13630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13630" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B13630" s="2" t="s">
         <v>6</v>
@@ -49827,21 +49818,21 @@
       <c r="A13647" s="8"/>
       <c r="B13647" s="9"/>
       <c r="C13647" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13648" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13648" s="8"/>
       <c r="B13648" s="9"/>
       <c r="C13648" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="13649" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13649" s="8"/>
       <c r="B13649" s="9"/>
       <c r="C13649" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13650" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49862,49 +49853,49 @@
       <c r="A13652" s="8"/>
       <c r="B13652" s="9"/>
       <c r="C13652" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="13653" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13653" s="8"/>
       <c r="B13653" s="9"/>
       <c r="C13653" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="13654" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13654" s="8"/>
       <c r="B13654" s="9"/>
       <c r="C13654" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13655" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13655" s="8"/>
       <c r="B13655" s="9"/>
       <c r="C13655" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="13656" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13656" s="8"/>
       <c r="B13656" s="9"/>
       <c r="C13656" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13657" s="8"/>
       <c r="B13657" s="9"/>
       <c r="C13657" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13658" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13658" s="8"/>
       <c r="B13658" s="9"/>
       <c r="C13658" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="13659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -49941,7 +49932,7 @@
     </row>
     <row r="13689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13689" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B13689" s="2" t="s">
         <v>22</v>
@@ -50005,7 +49996,7 @@
       </c>
       <c r="B13695" s="9"/>
       <c r="C13695" s="10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="13696" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50028,7 +50019,7 @@
     </row>
     <row r="13748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13748" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B13748" s="2" t="s">
         <v>22</v>
@@ -50099,21 +50090,21 @@
       <c r="A13755" s="8"/>
       <c r="B13755" s="9"/>
       <c r="C13755" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13756" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13756" s="8"/>
       <c r="B13756" s="9"/>
       <c r="C13756" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="13757" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13757" s="8"/>
       <c r="B13757" s="9"/>
       <c r="C13757" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13758" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50134,49 +50125,49 @@
       <c r="A13760" s="8"/>
       <c r="B13760" s="9"/>
       <c r="C13760" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="13761" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13761" s="8"/>
       <c r="B13761" s="9"/>
       <c r="C13761" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="13762" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13762" s="8"/>
       <c r="B13762" s="9"/>
       <c r="C13762" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13763" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13763" s="8"/>
       <c r="B13763" s="9"/>
       <c r="C13763" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="13764" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13764" s="8"/>
       <c r="B13764" s="9"/>
       <c r="C13764" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13765" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13765" s="8"/>
       <c r="B13765" s="9"/>
       <c r="C13765" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13766" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13766" s="8"/>
       <c r="B13766" s="9"/>
       <c r="C13766" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="13767" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50213,7 +50204,7 @@
     </row>
     <row r="13807" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13807" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B13807" s="2" t="s">
         <v>22</v>
@@ -50298,7 +50289,7 @@
     </row>
     <row r="13866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13866" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B13866" s="2" t="s">
         <v>15</v>
@@ -50372,7 +50363,7 @@
       </c>
       <c r="B13874" s="9"/>
       <c r="C13874" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="13875" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50395,7 +50386,7 @@
     </row>
     <row r="13925" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13925" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B13925" s="2" t="s">
         <v>24</v>
@@ -50498,14 +50489,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B13935" s="9"/>
-      <c r="C13935" s="35" t="s">
-        <v>544</v>
+      <c r="C13935" s="39" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="13936" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13936" s="8"/>
       <c r="B13936" s="9"/>
-      <c r="C13936" s="35"/>
+      <c r="C13936" s="39"/>
     </row>
     <row r="13937" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13937" s="8">
@@ -50527,7 +50518,7 @@
     </row>
     <row r="13984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13984" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B13984" s="2" t="s">
         <v>24</v>
@@ -50638,21 +50629,21 @@
       <c r="A13995" s="8"/>
       <c r="B13995" s="9"/>
       <c r="C13995" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13996" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13996" s="8"/>
       <c r="B13996" s="9"/>
       <c r="C13996" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="13997" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13997" s="8"/>
       <c r="B13997" s="9"/>
       <c r="C13997" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13998" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50673,49 +50664,49 @@
       <c r="A14000" s="8"/>
       <c r="B14000" s="9"/>
       <c r="C14000" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14001" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14001" s="8"/>
       <c r="B14001" s="9"/>
       <c r="C14001" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14002" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14002" s="8"/>
       <c r="B14002" s="9"/>
       <c r="C14002" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14003" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14003" s="8"/>
       <c r="B14003" s="9"/>
       <c r="C14003" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14004" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14004" s="8"/>
       <c r="B14004" s="9"/>
       <c r="C14004" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14005" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14005" s="8"/>
       <c r="B14005" s="9"/>
       <c r="C14005" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14006" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14006" s="8"/>
       <c r="B14006" s="9"/>
       <c r="C14006" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50752,7 +50743,7 @@
     </row>
     <row r="14043" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14043" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B14043" s="2" t="s">
         <v>6</v>
@@ -50874,7 +50865,7 @@
       </c>
       <c r="B14055" s="9"/>
       <c r="C14055" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="14056" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -50915,7 +50906,7 @@
     </row>
     <row r="14102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14102" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B14102" s="2" t="s">
         <v>19</v>
@@ -51046,21 +51037,21 @@
       <c r="A14115" s="8"/>
       <c r="B14115" s="9"/>
       <c r="C14115" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14116" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14116" s="8"/>
       <c r="B14116" s="9"/>
       <c r="C14116" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14117" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14117" s="8"/>
       <c r="B14117" s="9"/>
       <c r="C14117" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14118" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -51081,49 +51072,49 @@
       <c r="A14120" s="8"/>
       <c r="B14120" s="9"/>
       <c r="C14120" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14121" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14121" s="8"/>
       <c r="B14121" s="9"/>
       <c r="C14121" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14122" s="8"/>
       <c r="B14122" s="9"/>
       <c r="C14122" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14123" s="8"/>
       <c r="B14123" s="9"/>
       <c r="C14123" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14124" s="8"/>
       <c r="B14124" s="9"/>
       <c r="C14124" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14125" s="8"/>
       <c r="B14125" s="9"/>
       <c r="C14125" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14126" s="8"/>
       <c r="B14126" s="9"/>
       <c r="C14126" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14127" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -51160,7 +51151,7 @@
     </row>
     <row r="14161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14161" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B14161" s="2" t="s">
         <v>22</v>
@@ -51204,7 +51195,7 @@
       </c>
       <c r="B14165" s="9"/>
       <c r="C14165" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="14166" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -51214,14 +51205,14 @@
       <c r="B14166" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C14166" s="35" t="s">
+      <c r="C14166" s="39" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="14167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14167" s="8"/>
       <c r="B14167" s="9"/>
-      <c r="C14167" s="35"/>
+      <c r="C14167" s="39"/>
     </row>
     <row r="14168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14168" s="8">
@@ -51286,7 +51277,7 @@
     </row>
     <row r="14220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14220" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B14220" s="2" t="s">
         <v>19</v>
@@ -51473,21 +51464,21 @@
       <c r="A14241" s="8"/>
       <c r="B14241" s="9"/>
       <c r="C14241" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14242" s="8"/>
       <c r="B14242" s="9"/>
       <c r="C14242" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14243" s="8"/>
       <c r="B14243" s="9"/>
       <c r="C14243" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -51508,49 +51499,49 @@
       <c r="A14246" s="8"/>
       <c r="B14246" s="9"/>
       <c r="C14246" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14247" s="8"/>
       <c r="B14247" s="9"/>
       <c r="C14247" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14248" s="8"/>
       <c r="B14248" s="9"/>
       <c r="C14248" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14249" s="8"/>
       <c r="B14249" s="9"/>
       <c r="C14249" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14250" s="8"/>
       <c r="B14250" s="9"/>
       <c r="C14250" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14251" s="8"/>
       <c r="B14251" s="9"/>
       <c r="C14251" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14252" s="8"/>
       <c r="B14252" s="9"/>
       <c r="C14252" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -51587,7 +51578,7 @@
     </row>
     <row r="14279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14279" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B14279" s="2" t="s">
         <v>19</v>
@@ -51730,21 +51721,21 @@
       <c r="A14294" s="8"/>
       <c r="B14294" s="9"/>
       <c r="C14294" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14295" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14295" s="8"/>
       <c r="B14295" s="9"/>
       <c r="C14295" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14296" s="8"/>
       <c r="B14296" s="9"/>
       <c r="C14296" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -51765,49 +51756,49 @@
       <c r="A14299" s="8"/>
       <c r="B14299" s="9"/>
       <c r="C14299" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14300" s="8"/>
       <c r="B14300" s="9"/>
       <c r="C14300" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14301" s="8"/>
       <c r="B14301" s="9"/>
       <c r="C14301" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14302" s="8"/>
       <c r="B14302" s="9"/>
       <c r="C14302" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14303" s="8"/>
       <c r="B14303" s="9"/>
       <c r="C14303" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14304" s="8"/>
       <c r="B14304" s="9"/>
       <c r="C14304" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14305" s="8"/>
       <c r="B14305" s="9"/>
       <c r="C14305" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -51844,7 +51835,7 @@
     </row>
     <row r="14338" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14338" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B14338" s="2" t="s">
         <v>98</v>
@@ -52015,21 +52006,21 @@
       <c r="A14357" s="8"/>
       <c r="B14357" s="9"/>
       <c r="C14357" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14358" s="8"/>
       <c r="B14358" s="9"/>
       <c r="C14358" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14359" s="8"/>
       <c r="B14359" s="9"/>
       <c r="C14359" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52050,49 +52041,49 @@
       <c r="A14362" s="8"/>
       <c r="B14362" s="9"/>
       <c r="C14362" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14363" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14363" s="8"/>
       <c r="B14363" s="9"/>
       <c r="C14363" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14364" s="8"/>
       <c r="B14364" s="9"/>
       <c r="C14364" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14365" s="8"/>
       <c r="B14365" s="9"/>
       <c r="C14365" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14366" s="8"/>
       <c r="B14366" s="9"/>
       <c r="C14366" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14367" s="8"/>
       <c r="B14367" s="9"/>
       <c r="C14367" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14368" s="8"/>
       <c r="B14368" s="9"/>
       <c r="C14368" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52129,7 +52120,7 @@
     </row>
     <row r="14397" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14397" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B14397" s="2" t="s">
         <v>19</v>
@@ -52141,7 +52132,7 @@
     <row r="14398" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14398" s="4"/>
       <c r="B14398" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C14398" s="25"/>
     </row>
@@ -52251,7 +52242,7 @@
       </c>
       <c r="B14409" s="9"/>
       <c r="C14409" s="10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14410" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52274,7 +52265,7 @@
     </row>
     <row r="14456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14456" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B14456" s="2" t="s">
         <v>24</v>
@@ -52353,14 +52344,14 @@
         <v>3.1</v>
       </c>
       <c r="B14464" s="9"/>
-      <c r="C14464" s="35" t="s">
+      <c r="C14464" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="14465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14465" s="8"/>
       <c r="B14465" s="9"/>
-      <c r="C14465" s="35"/>
+      <c r="C14465" s="39"/>
     </row>
     <row r="14466" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14466" s="15">
@@ -52400,21 +52391,21 @@
       <c r="A14470" s="8"/>
       <c r="B14470" s="9"/>
       <c r="C14470" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14471" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14471" s="8"/>
       <c r="B14471" s="9"/>
       <c r="C14471" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14472" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14472" s="8"/>
       <c r="B14472" s="9"/>
       <c r="C14472" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14473" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52435,49 +52426,49 @@
       <c r="A14475" s="8"/>
       <c r="B14475" s="9"/>
       <c r="C14475" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14476" s="8"/>
       <c r="B14476" s="9"/>
       <c r="C14476" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14477" s="8"/>
       <c r="B14477" s="9"/>
       <c r="C14477" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14478" s="8"/>
       <c r="B14478" s="9"/>
       <c r="C14478" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14479" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14479" s="8"/>
       <c r="B14479" s="9"/>
       <c r="C14479" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14480" s="8"/>
       <c r="B14480" s="9"/>
       <c r="C14480" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14481" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14481" s="8"/>
       <c r="B14481" s="9"/>
       <c r="C14481" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52514,7 +52505,7 @@
     </row>
     <row r="14515" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14515" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B14515" s="2" t="s">
         <v>6</v>
@@ -52593,14 +52584,14 @@
         <v>3.1</v>
       </c>
       <c r="B14523" s="9"/>
-      <c r="C14523" s="35" t="s">
+      <c r="C14523" s="39" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="14524" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14524" s="8"/>
       <c r="B14524" s="9"/>
-      <c r="C14524" s="35"/>
+      <c r="C14524" s="39"/>
     </row>
     <row r="14525" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14525" s="8">
@@ -52651,7 +52642,7 @@
       </c>
       <c r="B14530" s="9"/>
       <c r="C14530" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="14531" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52692,7 +52683,7 @@
     </row>
     <row r="14574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14574" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B14574" s="2" t="s">
         <v>6</v>
@@ -52889,21 +52880,21 @@
       <c r="A14597" s="8"/>
       <c r="B14597" s="9"/>
       <c r="C14597" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14598" s="8"/>
       <c r="B14598" s="9"/>
       <c r="C14598" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14599" s="8"/>
       <c r="B14599" s="9"/>
       <c r="C14599" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14600" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52924,49 +52915,49 @@
       <c r="A14602" s="8"/>
       <c r="B14602" s="9"/>
       <c r="C14602" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14603" s="8"/>
       <c r="B14603" s="9"/>
       <c r="C14603" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14604" s="8"/>
       <c r="B14604" s="9"/>
       <c r="C14604" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14605" s="8"/>
       <c r="B14605" s="9"/>
       <c r="C14605" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14606" s="8"/>
       <c r="B14606" s="9"/>
       <c r="C14606" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14607" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14607" s="8"/>
       <c r="B14607" s="9"/>
       <c r="C14607" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14608" s="8"/>
       <c r="B14608" s="9"/>
       <c r="C14608" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14609" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53003,7 +52994,7 @@
     </row>
     <row r="14633" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14633" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B14633" s="2" t="s">
         <v>22</v>
@@ -53067,7 +53058,7 @@
       </c>
       <c r="B14639" s="9"/>
       <c r="C14639" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="14640" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53090,7 +53081,7 @@
     </row>
     <row r="14692" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14692" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B14692" s="2" t="s">
         <v>24</v>
@@ -53243,21 +53234,21 @@
       <c r="A14709" s="8"/>
       <c r="B14709" s="27"/>
       <c r="C14709" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14710" s="8"/>
       <c r="B14710" s="27"/>
       <c r="C14710" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14711" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14711" s="8"/>
       <c r="B14711" s="27"/>
       <c r="C14711" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14712" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53278,49 +53269,49 @@
       <c r="A14714" s="8"/>
       <c r="B14714" s="9"/>
       <c r="C14714" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14715" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14715" s="8"/>
       <c r="B14715" s="9"/>
       <c r="C14715" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14716" s="8"/>
       <c r="B14716" s="9"/>
       <c r="C14716" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14717" s="8"/>
       <c r="B14717" s="9"/>
       <c r="C14717" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14718" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14718" s="8"/>
       <c r="B14718" s="9"/>
       <c r="C14718" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14719" s="8"/>
       <c r="B14719" s="9"/>
       <c r="C14719" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14720" s="8"/>
       <c r="B14720" s="9"/>
       <c r="C14720" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53357,7 +53348,7 @@
     </row>
     <row r="14751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14751" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B14751" s="2" t="s">
         <v>24</v>
@@ -53431,7 +53422,7 @@
       </c>
       <c r="B14759" s="9"/>
       <c r="C14759" s="14" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14760" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53451,7 +53442,7 @@
       </c>
       <c r="B14761" s="27"/>
       <c r="C14761" s="27" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="14762" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53474,7 +53465,7 @@
     </row>
     <row r="14810" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14810" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B14810" s="2" t="s">
         <v>22</v>
@@ -53538,7 +53529,7 @@
       </c>
       <c r="B14816" s="27"/>
       <c r="C14816" s="38" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="14817" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53566,7 +53557,7 @@
     </row>
     <row r="14869" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14869" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B14869" s="2" t="s">
         <v>14</v>
@@ -53578,7 +53569,7 @@
     <row r="14870" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14870" s="4"/>
       <c r="B14870" s="36" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C14870" s="37"/>
     </row>
@@ -53668,7 +53659,7 @@
       </c>
       <c r="B14879" s="9"/>
       <c r="C14879" s="10" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="14880" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53688,14 +53679,14 @@
       </c>
       <c r="B14881" s="9"/>
       <c r="C14881" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14882" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14882" s="8"/>
       <c r="B14882" s="9"/>
       <c r="C14882" s="10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="14883" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53770,7 +53761,7 @@
     </row>
     <row r="14928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14928" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B14928" s="2" t="s">
         <v>24</v>
@@ -53923,21 +53914,21 @@
       <c r="A14945" s="8"/>
       <c r="B14945" s="9"/>
       <c r="C14945" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14946" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14946" s="8"/>
       <c r="B14946" s="9"/>
       <c r="C14946" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14947" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14947" s="8"/>
       <c r="B14947" s="9"/>
       <c r="C14947" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14948" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53958,49 +53949,49 @@
       <c r="A14950" s="8"/>
       <c r="B14950" s="9"/>
       <c r="C14950" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14951" s="8"/>
       <c r="B14951" s="9"/>
       <c r="C14951" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14952" s="8"/>
       <c r="B14952" s="9"/>
       <c r="C14952" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14953" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14953" s="8"/>
       <c r="B14953" s="9"/>
       <c r="C14953" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14954" s="8"/>
       <c r="B14954" s="9"/>
       <c r="C14954" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14955" s="8"/>
       <c r="B14955" s="9"/>
       <c r="C14955" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14956" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14956" s="8"/>
       <c r="B14956" s="9"/>
       <c r="C14956" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -54037,7 +54028,7 @@
     </row>
     <row r="14987" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14987" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B14987" s="2" t="s">
         <v>98</v>
@@ -54187,7 +54178,7 @@
       </c>
       <c r="B15003" s="9"/>
       <c r="C15003" s="10" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="15004" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -54228,7 +54219,7 @@
     </row>
     <row r="15046" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15046" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B15046" s="2" t="s">
         <v>19</v>
@@ -54373,21 +54364,21 @@
       <c r="A15061" s="8"/>
       <c r="B15061" s="9"/>
       <c r="C15061" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="15062" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15062" s="8"/>
       <c r="B15062" s="9"/>
       <c r="C15062" s="10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="15063" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15063" s="8"/>
       <c r="B15063" s="9"/>
       <c r="C15063" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="15064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -54408,49 +54399,49 @@
       <c r="A15066" s="8"/>
       <c r="B15066" s="9"/>
       <c r="C15066" s="10" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="15067" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15067" s="8"/>
       <c r="B15067" s="9"/>
       <c r="C15067" s="10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="15068" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15068" s="8"/>
       <c r="B15068" s="9"/>
       <c r="C15068" s="10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="15069" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15069" s="8"/>
       <c r="B15069" s="9"/>
       <c r="C15069" s="10" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="15070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15070" s="8"/>
       <c r="B15070" s="9"/>
       <c r="C15070" s="10" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="15071" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15071" s="8"/>
       <c r="B15071" s="9"/>
       <c r="C15071" s="10" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="15072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15072" s="8"/>
       <c r="B15072" s="9"/>
       <c r="C15072" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="15073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -54486,55 +54477,118 @@
       <c r="C15076" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="181">
-    <mergeCell ref="B14988:C14988"/>
-    <mergeCell ref="B15047:C15047"/>
-    <mergeCell ref="C14816:C14817"/>
-    <mergeCell ref="B14870:C14870"/>
-    <mergeCell ref="C14523:C14524"/>
-    <mergeCell ref="B14516:C14516"/>
-    <mergeCell ref="B14457:C14457"/>
-    <mergeCell ref="B14575:C14575"/>
-    <mergeCell ref="B14585:B14587"/>
-    <mergeCell ref="B14589:B14591"/>
-    <mergeCell ref="B13631:C13631"/>
-    <mergeCell ref="C13935:C13936"/>
-    <mergeCell ref="B14044:C14044"/>
-    <mergeCell ref="C14166:C14167"/>
-    <mergeCell ref="B14221:C14221"/>
-    <mergeCell ref="C14464:C14465"/>
-    <mergeCell ref="C13223:C13224"/>
-    <mergeCell ref="B13277:C13277"/>
-    <mergeCell ref="C12581:C12582"/>
-    <mergeCell ref="B13100:C13100"/>
-    <mergeCell ref="C13172:C13173"/>
-    <mergeCell ref="C13463:C13464"/>
-    <mergeCell ref="B13291:B13293"/>
-    <mergeCell ref="C12576:C12577"/>
-    <mergeCell ref="B12628:C12628"/>
-    <mergeCell ref="C12635:C12636"/>
-    <mergeCell ref="B12510:C12510"/>
-    <mergeCell ref="B12520:B12522"/>
-    <mergeCell ref="C12405:C12406"/>
-    <mergeCell ref="B12451:C12451"/>
-    <mergeCell ref="C12468:C12469"/>
-    <mergeCell ref="C13056:C13057"/>
-    <mergeCell ref="C12820:C12821"/>
-    <mergeCell ref="B12982:C12982"/>
-    <mergeCell ref="B12994:B12996"/>
-    <mergeCell ref="B12687:C12687"/>
-    <mergeCell ref="B12701:B12703"/>
-    <mergeCell ref="B12697:B12699"/>
-    <mergeCell ref="C12708:C12709"/>
-    <mergeCell ref="C12278:C12279"/>
-    <mergeCell ref="B12333:C12333"/>
-    <mergeCell ref="C12352:C12353"/>
-    <mergeCell ref="C12106:C12107"/>
-    <mergeCell ref="B12156:C12156"/>
-    <mergeCell ref="C12226:C12227"/>
-    <mergeCell ref="C11758:C11759"/>
-    <mergeCell ref="C11866:C11867"/>
-    <mergeCell ref="C12047:C12048"/>
+  <mergeCells count="182">
+    <mergeCell ref="C8741:C8742"/>
+    <mergeCell ref="B7627:B7629"/>
+    <mergeCell ref="C8502:C8503"/>
+    <mergeCell ref="B8557:C8557"/>
+    <mergeCell ref="B8675:C8675"/>
+    <mergeCell ref="B7613:C7613"/>
+    <mergeCell ref="B5784:C5784"/>
+    <mergeCell ref="B7672:C7672"/>
+    <mergeCell ref="B6020:C6020"/>
+    <mergeCell ref="C6853:C6854"/>
+    <mergeCell ref="C6912:C6913"/>
+    <mergeCell ref="C6971:C6972"/>
+    <mergeCell ref="B6964:C6964"/>
+    <mergeCell ref="C7451:C7452"/>
+    <mergeCell ref="B7436:C7436"/>
+    <mergeCell ref="C7558:C7559"/>
+    <mergeCell ref="B7209:B7211"/>
+    <mergeCell ref="B7318:C7318"/>
+    <mergeCell ref="C6978:C6979"/>
+    <mergeCell ref="B7023:C7023"/>
+    <mergeCell ref="B7033:B7035"/>
+    <mergeCell ref="B7037:B7039"/>
+    <mergeCell ref="B5607:C5607"/>
+    <mergeCell ref="B5430:C5430"/>
+    <mergeCell ref="B5489:C5489"/>
+    <mergeCell ref="B5548:C5548"/>
+    <mergeCell ref="C5563:C5564"/>
+    <mergeCell ref="B6669:C6669"/>
+    <mergeCell ref="B6787:C6787"/>
+    <mergeCell ref="C6031:C6032"/>
+    <mergeCell ref="B6492:C6492"/>
+    <mergeCell ref="C6503:C6504"/>
+    <mergeCell ref="C6614:C6615"/>
+    <mergeCell ref="B5739:B5741"/>
+    <mergeCell ref="B5725:C5725"/>
+    <mergeCell ref="C5024:C5025"/>
+    <mergeCell ref="B4781:C4781"/>
+    <mergeCell ref="C4969:C4970"/>
+    <mergeCell ref="B4899:C4899"/>
+    <mergeCell ref="C4615:C4616"/>
+    <mergeCell ref="B5135:C5135"/>
+    <mergeCell ref="B5145:B5147"/>
+    <mergeCell ref="B5149:B5151"/>
+    <mergeCell ref="B5076:C5076"/>
+    <mergeCell ref="C5083:C5084"/>
+    <mergeCell ref="C5090:C5091"/>
+    <mergeCell ref="B3365:C3365"/>
+    <mergeCell ref="C3675:C3676"/>
+    <mergeCell ref="B3257:B3259"/>
+    <mergeCell ref="B3261:B3263"/>
+    <mergeCell ref="B3247:C3247"/>
+    <mergeCell ref="B4604:C4604"/>
+    <mergeCell ref="B4663:C4663"/>
+    <mergeCell ref="C4726:C4727"/>
+    <mergeCell ref="B3660:C3660"/>
+    <mergeCell ref="B3837:C3837"/>
+    <mergeCell ref="B3896:C3896"/>
+    <mergeCell ref="C4143:C4144"/>
+    <mergeCell ref="B4191:C4191"/>
+    <mergeCell ref="B4014:C4014"/>
+    <mergeCell ref="C4025:C4026"/>
+    <mergeCell ref="B4132:C4132"/>
+    <mergeCell ref="B3851:B3853"/>
+    <mergeCell ref="B2775:C2775"/>
+    <mergeCell ref="C2838:C2839"/>
+    <mergeCell ref="B2893:C2893"/>
+    <mergeCell ref="B2657:C2657"/>
+    <mergeCell ref="B2716:C2716"/>
+    <mergeCell ref="C2727:C2728"/>
+    <mergeCell ref="C3202:C3203"/>
+    <mergeCell ref="B3188:C3188"/>
+    <mergeCell ref="C3077:C3078"/>
+    <mergeCell ref="C3136:C3137"/>
+    <mergeCell ref="C3195:C3196"/>
+    <mergeCell ref="B3011:C3011"/>
+    <mergeCell ref="C2255:C2256"/>
+    <mergeCell ref="B2244:C2244"/>
+    <mergeCell ref="B1949:C1949"/>
+    <mergeCell ref="B1890:C1890"/>
+    <mergeCell ref="B1831:C1831"/>
+    <mergeCell ref="B1772:C1772"/>
+    <mergeCell ref="B1713:C1713"/>
+    <mergeCell ref="C1787:C1788"/>
+    <mergeCell ref="B1654:C1654"/>
+    <mergeCell ref="B1963:B1965"/>
+    <mergeCell ref="B1477:C1477"/>
+    <mergeCell ref="B1359:C1359"/>
+    <mergeCell ref="B1300:C1300"/>
+    <mergeCell ref="B887:C887"/>
+    <mergeCell ref="C950:C951"/>
+    <mergeCell ref="B1064:C1064"/>
+    <mergeCell ref="C1248:C1249"/>
+    <mergeCell ref="C367:C368"/>
+    <mergeCell ref="B415:C415"/>
+    <mergeCell ref="B710:C710"/>
+    <mergeCell ref="B828:C828"/>
+    <mergeCell ref="C839:C840"/>
+    <mergeCell ref="C1307:C1308"/>
+    <mergeCell ref="C1314:C1315"/>
+    <mergeCell ref="B1369:B1371"/>
+    <mergeCell ref="B1373:B1375"/>
+    <mergeCell ref="B1123:C1123"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B1182:C1182"/>
+    <mergeCell ref="B1005:C1005"/>
+    <mergeCell ref="A145:C145"/>
+    <mergeCell ref="A24:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="B179:C179"/>
+    <mergeCell ref="B75:B77"/>
     <mergeCell ref="C8800:C8801"/>
     <mergeCell ref="C11516:C11517"/>
     <mergeCell ref="C11575:C11576"/>
@@ -54556,118 +54610,56 @@
     <mergeCell ref="B10445:C10445"/>
     <mergeCell ref="B8925:B8927"/>
     <mergeCell ref="B8921:B8923"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B1182:C1182"/>
-    <mergeCell ref="B1005:C1005"/>
-    <mergeCell ref="A145:C145"/>
-    <mergeCell ref="A24:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="B179:C179"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B1477:C1477"/>
-    <mergeCell ref="B1359:C1359"/>
-    <mergeCell ref="B1300:C1300"/>
-    <mergeCell ref="B887:C887"/>
-    <mergeCell ref="C950:C951"/>
-    <mergeCell ref="B1064:C1064"/>
-    <mergeCell ref="C1248:C1249"/>
-    <mergeCell ref="C367:C368"/>
-    <mergeCell ref="B415:C415"/>
-    <mergeCell ref="B710:C710"/>
-    <mergeCell ref="B828:C828"/>
-    <mergeCell ref="C839:C840"/>
-    <mergeCell ref="C1307:C1308"/>
-    <mergeCell ref="C1314:C1315"/>
-    <mergeCell ref="B1369:B1371"/>
-    <mergeCell ref="B1373:B1375"/>
-    <mergeCell ref="B1123:C1123"/>
-    <mergeCell ref="C2255:C2256"/>
-    <mergeCell ref="B2244:C2244"/>
-    <mergeCell ref="B1949:C1949"/>
-    <mergeCell ref="B1890:C1890"/>
-    <mergeCell ref="B1831:C1831"/>
-    <mergeCell ref="B1772:C1772"/>
-    <mergeCell ref="B1713:C1713"/>
-    <mergeCell ref="C1787:C1788"/>
-    <mergeCell ref="B1654:C1654"/>
-    <mergeCell ref="B1963:B1965"/>
-    <mergeCell ref="B2775:C2775"/>
-    <mergeCell ref="C2838:C2839"/>
-    <mergeCell ref="B2893:C2893"/>
-    <mergeCell ref="B2657:C2657"/>
-    <mergeCell ref="B2716:C2716"/>
-    <mergeCell ref="C2727:C2728"/>
-    <mergeCell ref="C3202:C3203"/>
-    <mergeCell ref="B3188:C3188"/>
-    <mergeCell ref="C3077:C3078"/>
-    <mergeCell ref="C3136:C3137"/>
-    <mergeCell ref="C3195:C3196"/>
-    <mergeCell ref="B3011:C3011"/>
-    <mergeCell ref="B3365:C3365"/>
-    <mergeCell ref="C3675:C3676"/>
-    <mergeCell ref="B3257:B3259"/>
-    <mergeCell ref="B3261:B3263"/>
-    <mergeCell ref="B3247:C3247"/>
-    <mergeCell ref="B4604:C4604"/>
-    <mergeCell ref="B4663:C4663"/>
-    <mergeCell ref="C4726:C4727"/>
-    <mergeCell ref="B3660:C3660"/>
-    <mergeCell ref="B3837:C3837"/>
-    <mergeCell ref="B3896:C3896"/>
-    <mergeCell ref="C4143:C4144"/>
-    <mergeCell ref="B4191:C4191"/>
-    <mergeCell ref="B4014:C4014"/>
-    <mergeCell ref="C4025:C4026"/>
-    <mergeCell ref="B4132:C4132"/>
-    <mergeCell ref="B3851:B3853"/>
-    <mergeCell ref="C5024:C5025"/>
-    <mergeCell ref="B4781:C4781"/>
-    <mergeCell ref="C4969:C4970"/>
-    <mergeCell ref="B4899:C4899"/>
-    <mergeCell ref="C4615:C4616"/>
-    <mergeCell ref="B5135:C5135"/>
-    <mergeCell ref="B5145:B5147"/>
-    <mergeCell ref="B5149:B5151"/>
-    <mergeCell ref="B5076:C5076"/>
-    <mergeCell ref="C5083:C5084"/>
-    <mergeCell ref="C5090:C5091"/>
-    <mergeCell ref="B5607:C5607"/>
-    <mergeCell ref="B5430:C5430"/>
-    <mergeCell ref="B5489:C5489"/>
-    <mergeCell ref="B5548:C5548"/>
-    <mergeCell ref="C5563:C5564"/>
-    <mergeCell ref="B6669:C6669"/>
-    <mergeCell ref="B6787:C6787"/>
-    <mergeCell ref="C6031:C6032"/>
-    <mergeCell ref="B6492:C6492"/>
-    <mergeCell ref="C6503:C6504"/>
-    <mergeCell ref="C6614:C6615"/>
-    <mergeCell ref="B5739:B5741"/>
-    <mergeCell ref="B5725:C5725"/>
     <mergeCell ref="C8859:C8860"/>
     <mergeCell ref="B8911:C8911"/>
-    <mergeCell ref="C8502:C8503"/>
-    <mergeCell ref="B8557:C8557"/>
-    <mergeCell ref="B8675:C8675"/>
-    <mergeCell ref="B7613:C7613"/>
-    <mergeCell ref="B5784:C5784"/>
-    <mergeCell ref="B7672:C7672"/>
-    <mergeCell ref="B6020:C6020"/>
-    <mergeCell ref="C6853:C6854"/>
-    <mergeCell ref="C6912:C6913"/>
-    <mergeCell ref="C6971:C6972"/>
-    <mergeCell ref="B6964:C6964"/>
-    <mergeCell ref="C7451:C7452"/>
-    <mergeCell ref="B7436:C7436"/>
-    <mergeCell ref="C7558:C7559"/>
-    <mergeCell ref="B7209:B7211"/>
-    <mergeCell ref="B7318:C7318"/>
-    <mergeCell ref="C6978:C6979"/>
-    <mergeCell ref="B7023:C7023"/>
-    <mergeCell ref="B7033:B7035"/>
-    <mergeCell ref="B7037:B7039"/>
-    <mergeCell ref="C8741:C8742"/>
+    <mergeCell ref="C12278:C12279"/>
+    <mergeCell ref="B12333:C12333"/>
+    <mergeCell ref="C12352:C12353"/>
+    <mergeCell ref="C12106:C12107"/>
+    <mergeCell ref="B12156:C12156"/>
+    <mergeCell ref="C12226:C12227"/>
+    <mergeCell ref="C11758:C11759"/>
+    <mergeCell ref="C11866:C11867"/>
+    <mergeCell ref="C12047:C12048"/>
+    <mergeCell ref="C12576:C12577"/>
+    <mergeCell ref="B12628:C12628"/>
+    <mergeCell ref="C12635:C12636"/>
+    <mergeCell ref="B12510:C12510"/>
+    <mergeCell ref="B12520:B12522"/>
+    <mergeCell ref="C12405:C12406"/>
+    <mergeCell ref="B12451:C12451"/>
+    <mergeCell ref="C12468:C12469"/>
+    <mergeCell ref="C13056:C13057"/>
+    <mergeCell ref="C12820:C12821"/>
+    <mergeCell ref="B12982:C12982"/>
+    <mergeCell ref="B12994:B12996"/>
+    <mergeCell ref="B12687:C12687"/>
+    <mergeCell ref="B12701:B12703"/>
+    <mergeCell ref="B12697:B12699"/>
+    <mergeCell ref="C12708:C12709"/>
+    <mergeCell ref="B13631:C13631"/>
+    <mergeCell ref="C13935:C13936"/>
+    <mergeCell ref="B14044:C14044"/>
+    <mergeCell ref="C14166:C14167"/>
+    <mergeCell ref="B14221:C14221"/>
+    <mergeCell ref="C14464:C14465"/>
+    <mergeCell ref="C13223:C13224"/>
+    <mergeCell ref="B13277:C13277"/>
+    <mergeCell ref="C12581:C12582"/>
+    <mergeCell ref="B13100:C13100"/>
+    <mergeCell ref="C13172:C13173"/>
+    <mergeCell ref="C13463:C13464"/>
+    <mergeCell ref="B13291:B13293"/>
+    <mergeCell ref="B14988:C14988"/>
+    <mergeCell ref="B15047:C15047"/>
+    <mergeCell ref="C14816:C14817"/>
+    <mergeCell ref="B14870:C14870"/>
+    <mergeCell ref="C14523:C14524"/>
+    <mergeCell ref="B14516:C14516"/>
+    <mergeCell ref="B14457:C14457"/>
+    <mergeCell ref="B14575:C14575"/>
+    <mergeCell ref="B14585:B14587"/>
+    <mergeCell ref="B14589:B14591"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>

--- a/Research/Instructions/Ricoh 5A22 Instructions Emulation SNES.xlsx
+++ b/Research/Instructions/Ricoh 5A22 Instructions Emulation SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FEE5B5-15AA-40C4-BE9A-9C7689BF4152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99E027D-5A34-4539-A70D-49A0071B6761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -14268,17 +14268,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -14884,10 +14884,10 @@
     </row>
     <row r="61" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4"/>
-      <c r="B61" s="36" t="s">
+      <c r="B61" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="C61" s="37"/>
+      <c r="C61" s="39"/>
     </row>
     <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
@@ -15008,7 +15008,7 @@
       <c r="A75" s="8">
         <v>5.2</v>
       </c>
-      <c r="B75" s="38" t="s">
+      <c r="B75" s="37" t="s">
         <v>584</v>
       </c>
       <c r="C75" s="14" t="s">
@@ -15017,12 +15017,12 @@
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="8"/>
-      <c r="B76" s="38"/>
+      <c r="B76" s="37"/>
       <c r="C76" s="14"/>
     </row>
     <row r="77" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="8"/>
-      <c r="B77" s="38"/>
+      <c r="B77" s="37"/>
       <c r="C77" s="14"/>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15308,10 +15308,10 @@
     </row>
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4"/>
-      <c r="B179" s="36" t="s">
+      <c r="B179" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="C179" s="37"/>
+      <c r="C179" s="39"/>
     </row>
     <row r="180" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
@@ -15817,14 +15817,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B367" s="9"/>
-      <c r="C367" s="39" t="s">
+      <c r="C367" s="36" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="8"/>
       <c r="B368" s="9"/>
-      <c r="C368" s="39"/>
+      <c r="C368" s="36"/>
     </row>
     <row r="369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="18">
@@ -15875,10 +15875,10 @@
     </row>
     <row r="415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="4"/>
-      <c r="B415" s="36" t="s">
+      <c r="B415" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="C415" s="37"/>
+      <c r="C415" s="39"/>
     </row>
     <row r="416" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="12" t="s">
@@ -16446,10 +16446,10 @@
     </row>
     <row r="710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="4"/>
-      <c r="B710" s="36" t="s">
+      <c r="B710" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C710" s="37"/>
+      <c r="C710" s="39"/>
     </row>
     <row r="711" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="12" t="s">
@@ -16736,10 +16736,10 @@
     </row>
     <row r="828" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="4"/>
-      <c r="B828" s="36" t="s">
+      <c r="B828" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C828" s="37"/>
+      <c r="C828" s="39"/>
     </row>
     <row r="829" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="12" t="s">
@@ -16846,14 +16846,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B839" s="9"/>
-      <c r="C839" s="39" t="s">
+      <c r="C839" s="36" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="8"/>
       <c r="B840" s="9"/>
-      <c r="C840" s="39"/>
+      <c r="C840" s="36"/>
     </row>
     <row r="841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="18">
@@ -16904,10 +16904,10 @@
     </row>
     <row r="887" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="4"/>
-      <c r="B887" s="36" t="s">
+      <c r="B887" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="C887" s="37"/>
+      <c r="C887" s="39"/>
     </row>
     <row r="888" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="12" t="s">
@@ -17094,14 +17094,14 @@
       <c r="B950" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C950" s="39" t="s">
+      <c r="C950" s="36" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="8"/>
       <c r="B951" s="9"/>
-      <c r="C951" s="39"/>
+      <c r="C951" s="36"/>
     </row>
     <row r="952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="8">
@@ -17177,10 +17177,10 @@
     </row>
     <row r="1005" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="4"/>
-      <c r="B1005" s="36" t="s">
+      <c r="B1005" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C1005" s="37"/>
+      <c r="C1005" s="39"/>
     </row>
     <row r="1006" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="12" t="s">
@@ -17380,10 +17380,10 @@
     </row>
     <row r="1064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="4"/>
-      <c r="B1064" s="36" t="s">
+      <c r="B1064" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="C1064" s="37"/>
+      <c r="C1064" s="39"/>
     </row>
     <row r="1065" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1065" s="12" t="s">
@@ -17539,10 +17539,10 @@
     </row>
     <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="4"/>
-      <c r="B1123" s="36" t="s">
+      <c r="B1123" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="C1123" s="37"/>
+      <c r="C1123" s="39"/>
     </row>
     <row r="1124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1124" s="12" t="s">
@@ -17726,10 +17726,10 @@
     </row>
     <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="4"/>
-      <c r="B1182" s="36" t="s">
+      <c r="B1182" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C1182" s="37"/>
+      <c r="C1182" s="39"/>
     </row>
     <row r="1183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1183" s="12" t="s">
@@ -17953,14 +17953,14 @@
         <v>3.1</v>
       </c>
       <c r="B1248" s="9"/>
-      <c r="C1248" s="39" t="s">
+      <c r="C1248" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="1249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1249" s="8"/>
       <c r="B1249" s="9"/>
-      <c r="C1249" s="39"/>
+      <c r="C1249" s="36"/>
     </row>
     <row r="1250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1250" s="15">
@@ -18027,10 +18027,10 @@
     </row>
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="4"/>
-      <c r="B1300" s="36" t="s">
+      <c r="B1300" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="C1300" s="37"/>
+      <c r="C1300" s="39"/>
     </row>
     <row r="1301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1301" s="12" t="s">
@@ -18095,14 +18095,14 @@
         <v>3.1</v>
       </c>
       <c r="B1307" s="9"/>
-      <c r="C1307" s="39" t="s">
+      <c r="C1307" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="1308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1308" s="8"/>
       <c r="B1308" s="9"/>
-      <c r="C1308" s="39"/>
+      <c r="C1308" s="36"/>
     </row>
     <row r="1309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1309" s="15">
@@ -18152,14 +18152,14 @@
         <v>6.1</v>
       </c>
       <c r="B1314" s="9"/>
-      <c r="C1314" s="39" t="s">
+      <c r="C1314" s="36" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="1315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1315" s="8"/>
       <c r="B1315" s="9"/>
-      <c r="C1315" s="39"/>
+      <c r="C1315" s="36"/>
     </row>
     <row r="1316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1316" s="18">
@@ -18210,10 +18210,10 @@
     </row>
     <row r="1359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="4"/>
-      <c r="B1359" s="36" t="s">
+      <c r="B1359" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C1359" s="37"/>
+      <c r="C1359" s="39"/>
     </row>
     <row r="1360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1360" s="12" t="s">
@@ -18304,7 +18304,7 @@
       <c r="A1369" s="8">
         <v>4.2</v>
       </c>
-      <c r="B1369" s="38" t="s">
+      <c r="B1369" s="37" t="s">
         <v>156</v>
       </c>
       <c r="C1369" s="14" t="s">
@@ -18313,12 +18313,12 @@
     </row>
     <row r="1370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1370" s="8"/>
-      <c r="B1370" s="38"/>
+      <c r="B1370" s="37"/>
       <c r="C1370" s="14"/>
     </row>
     <row r="1371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1371" s="8"/>
-      <c r="B1371" s="38"/>
+      <c r="B1371" s="37"/>
       <c r="C1371" s="14"/>
     </row>
     <row r="1372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18332,7 +18332,7 @@
       <c r="A1373" s="8">
         <v>5.2</v>
       </c>
-      <c r="B1373" s="38" t="s">
+      <c r="B1373" s="37" t="s">
         <v>157</v>
       </c>
       <c r="C1373" s="10" t="s">
@@ -18341,12 +18341,12 @@
     </row>
     <row r="1374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1374" s="8"/>
-      <c r="B1374" s="38"/>
+      <c r="B1374" s="37"/>
       <c r="C1374" s="10"/>
     </row>
     <row r="1375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1375" s="8"/>
-      <c r="B1375" s="38"/>
+      <c r="B1375" s="37"/>
       <c r="C1375" s="10"/>
     </row>
     <row r="1376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18510,10 +18510,10 @@
     </row>
     <row r="1477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1477" s="4"/>
-      <c r="B1477" s="36" t="s">
+      <c r="B1477" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C1477" s="37"/>
+      <c r="C1477" s="39"/>
     </row>
     <row r="1478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1478" s="12" t="s">
@@ -18853,10 +18853,10 @@
     </row>
     <row r="1654" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1654" s="4"/>
-      <c r="B1654" s="36" t="s">
+      <c r="B1654" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C1654" s="37"/>
+      <c r="C1654" s="39"/>
     </row>
     <row r="1655" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1655" s="12" t="s">
@@ -19016,10 +19016,10 @@
     </row>
     <row r="1713" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1713" s="4"/>
-      <c r="B1713" s="36" t="s">
+      <c r="B1713" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="C1713" s="37"/>
+      <c r="C1713" s="39"/>
     </row>
     <row r="1714" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1714" s="12" t="s">
@@ -19185,10 +19185,10 @@
     </row>
     <row r="1772" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1772" s="4"/>
-      <c r="B1772" s="36" t="s">
+      <c r="B1772" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="C1772" s="37"/>
+      <c r="C1772" s="39"/>
     </row>
     <row r="1773" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1773" s="12" t="s">
@@ -19323,14 +19323,14 @@
         <v>6.1</v>
       </c>
       <c r="B1787" s="9"/>
-      <c r="C1787" s="39" t="s">
+      <c r="C1787" s="36" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="1788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1788" s="8"/>
       <c r="B1788" s="9"/>
-      <c r="C1788" s="39"/>
+      <c r="C1788" s="36"/>
     </row>
     <row r="1789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1789" s="18">
@@ -19381,10 +19381,10 @@
     </row>
     <row r="1831" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1831" s="4"/>
-      <c r="B1831" s="36" t="s">
+      <c r="B1831" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="C1831" s="37"/>
+      <c r="C1831" s="39"/>
     </row>
     <row r="1832" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1832" s="12" t="s">
@@ -19542,10 +19542,10 @@
     </row>
     <row r="1890" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1890" s="4"/>
-      <c r="B1890" s="36" t="s">
+      <c r="B1890" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="C1890" s="37"/>
+      <c r="C1890" s="39"/>
     </row>
     <row r="1891" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1891" s="12" t="s">
@@ -19707,10 +19707,10 @@
     </row>
     <row r="1949" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1949" s="4"/>
-      <c r="B1949" s="36" t="s">
+      <c r="B1949" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="C1949" s="37"/>
+      <c r="C1949" s="39"/>
     </row>
     <row r="1950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1950" s="12" t="s">
@@ -19831,7 +19831,7 @@
       <c r="A1963" s="8">
         <v>5.2</v>
       </c>
-      <c r="B1963" s="38" t="s">
+      <c r="B1963" s="37" t="s">
         <v>584</v>
       </c>
       <c r="C1963" s="14" t="s">
@@ -19840,12 +19840,12 @@
     </row>
     <row r="1964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1964" s="8"/>
-      <c r="B1964" s="38"/>
+      <c r="B1964" s="37"/>
       <c r="C1964" s="14"/>
     </row>
     <row r="1965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1965" s="8"/>
-      <c r="B1965" s="38"/>
+      <c r="B1965" s="37"/>
       <c r="C1965" s="14"/>
     </row>
     <row r="1966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20477,10 +20477,10 @@
     </row>
     <row r="2244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2244" s="4"/>
-      <c r="B2244" s="36" t="s">
+      <c r="B2244" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C2244" s="37"/>
+      <c r="C2244" s="39"/>
     </row>
     <row r="2245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2245" s="12" t="s">
@@ -20583,14 +20583,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2255" s="9"/>
-      <c r="C2255" s="39" t="s">
+      <c r="C2255" s="36" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="2256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2256" s="8"/>
       <c r="B2256" s="9"/>
-      <c r="C2256" s="39"/>
+      <c r="C2256" s="36"/>
     </row>
     <row r="2257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2257" s="18">
@@ -21369,10 +21369,10 @@
     </row>
     <row r="2657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2657" s="4"/>
-      <c r="B2657" s="36" t="s">
+      <c r="B2657" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C2657" s="37"/>
+      <c r="C2657" s="39"/>
     </row>
     <row r="2658" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2658" s="12" t="s">
@@ -21496,10 +21496,10 @@
     </row>
     <row r="2716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2716" s="4"/>
-      <c r="B2716" s="36" t="s">
+      <c r="B2716" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C2716" s="37"/>
+      <c r="C2716" s="39"/>
     </row>
     <row r="2717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2717" s="12" t="s">
@@ -21606,14 +21606,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B2727" s="9"/>
-      <c r="C2727" s="39" t="s">
+      <c r="C2727" s="36" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="2728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2728" s="8"/>
       <c r="B2728" s="9"/>
-      <c r="C2728" s="39"/>
+      <c r="C2728" s="36"/>
     </row>
     <row r="2729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2729" s="18">
@@ -21664,10 +21664,10 @@
     </row>
     <row r="2775" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2775" s="4"/>
-      <c r="B2775" s="36" t="s">
+      <c r="B2775" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="C2775" s="37"/>
+      <c r="C2775" s="39"/>
     </row>
     <row r="2776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2776" s="12" t="s">
@@ -21854,14 +21854,14 @@
       <c r="B2838" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C2838" s="39" t="s">
+      <c r="C2838" s="36" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="2839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2839" s="8"/>
       <c r="B2839" s="9"/>
-      <c r="C2839" s="39"/>
+      <c r="C2839" s="36"/>
     </row>
     <row r="2840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2840" s="8">
@@ -21937,10 +21937,10 @@
     </row>
     <row r="2893" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2893" s="4"/>
-      <c r="B2893" s="36" t="s">
+      <c r="B2893" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C2893" s="37"/>
+      <c r="C2893" s="39"/>
     </row>
     <row r="2894" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2894" s="12" t="s">
@@ -22299,10 +22299,10 @@
     </row>
     <row r="3011" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3011" s="4"/>
-      <c r="B3011" s="36" t="s">
+      <c r="B3011" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="C3011" s="37"/>
+      <c r="C3011" s="39"/>
     </row>
     <row r="3012" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3012" s="12" t="s">
@@ -22554,14 +22554,14 @@
         <v>3.1</v>
       </c>
       <c r="B3077" s="9"/>
-      <c r="C3077" s="39" t="s">
+      <c r="C3077" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="3078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3078" s="8"/>
       <c r="B3078" s="9"/>
-      <c r="C3078" s="39"/>
+      <c r="C3078" s="36"/>
     </row>
     <row r="3079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3079" s="15">
@@ -22706,14 +22706,14 @@
         <v>3.1</v>
       </c>
       <c r="B3136" s="9"/>
-      <c r="C3136" s="39" t="s">
+      <c r="C3136" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="3137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3137" s="8"/>
       <c r="B3137" s="9"/>
-      <c r="C3137" s="39"/>
+      <c r="C3137" s="36"/>
     </row>
     <row r="3138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3138" s="15">
@@ -22780,10 +22780,10 @@
     </row>
     <row r="3188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3188" s="4"/>
-      <c r="B3188" s="36" t="s">
+      <c r="B3188" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="C3188" s="37"/>
+      <c r="C3188" s="39"/>
     </row>
     <row r="3189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3189" s="12" t="s">
@@ -22848,14 +22848,14 @@
         <v>3.1</v>
       </c>
       <c r="B3195" s="9"/>
-      <c r="C3195" s="39" t="s">
+      <c r="C3195" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="3196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3196" s="8"/>
       <c r="B3196" s="9"/>
-      <c r="C3196" s="39"/>
+      <c r="C3196" s="36"/>
     </row>
     <row r="3197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3197" s="15">
@@ -22905,14 +22905,14 @@
         <v>6.1</v>
       </c>
       <c r="B3202" s="9"/>
-      <c r="C3202" s="39" t="s">
+      <c r="C3202" s="36" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="3203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3203" s="8"/>
       <c r="B3203" s="9"/>
-      <c r="C3203" s="39"/>
+      <c r="C3203" s="36"/>
     </row>
     <row r="3204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3204" s="18">
@@ -22973,10 +22973,10 @@
     </row>
     <row r="3247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3247" s="4"/>
-      <c r="B3247" s="36" t="s">
+      <c r="B3247" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C3247" s="37"/>
+      <c r="C3247" s="39"/>
     </row>
     <row r="3248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3248" s="12" t="s">
@@ -23067,7 +23067,7 @@
       <c r="A3257" s="8">
         <v>4.2</v>
       </c>
-      <c r="B3257" s="38" t="s">
+      <c r="B3257" s="37" t="s">
         <v>156</v>
       </c>
       <c r="C3257" s="10" t="s">
@@ -23076,12 +23076,12 @@
     </row>
     <row r="3258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3258" s="8"/>
-      <c r="B3258" s="38"/>
+      <c r="B3258" s="37"/>
       <c r="C3258" s="10"/>
     </row>
     <row r="3259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3259" s="8"/>
-      <c r="B3259" s="38"/>
+      <c r="B3259" s="37"/>
       <c r="C3259" s="10"/>
     </row>
     <row r="3260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23095,7 +23095,7 @@
       <c r="A3261" s="8">
         <v>5.2</v>
       </c>
-      <c r="B3261" s="38" t="s">
+      <c r="B3261" s="37" t="s">
         <v>157</v>
       </c>
       <c r="C3261" s="10" t="s">
@@ -23104,12 +23104,12 @@
     </row>
     <row r="3262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3262" s="8"/>
-      <c r="B3262" s="38"/>
+      <c r="B3262" s="37"/>
       <c r="C3262" s="10"/>
     </row>
     <row r="3263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3263" s="8"/>
-      <c r="B3263" s="38"/>
+      <c r="B3263" s="37"/>
       <c r="C3263" s="10"/>
     </row>
     <row r="3264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23273,10 +23273,10 @@
     </row>
     <row r="3365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3365" s="4"/>
-      <c r="B3365" s="36" t="s">
+      <c r="B3365" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C3365" s="37"/>
+      <c r="C3365" s="39"/>
     </row>
     <row r="3366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3366" s="12" t="s">
@@ -23954,10 +23954,10 @@
     </row>
     <row r="3660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3660" s="4"/>
-      <c r="B3660" s="36" t="s">
+      <c r="B3660" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="C3660" s="37"/>
+      <c r="C3660" s="39"/>
     </row>
     <row r="3661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3661" s="12" t="s">
@@ -24092,14 +24092,14 @@
         <v>6.1</v>
       </c>
       <c r="B3675" s="9"/>
-      <c r="C3675" s="39" t="s">
+      <c r="C3675" s="36" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="3676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3676" s="8"/>
       <c r="B3676" s="9"/>
-      <c r="C3676" s="39"/>
+      <c r="C3676" s="36"/>
     </row>
     <row r="3677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3677" s="18">
@@ -24466,10 +24466,10 @@
     </row>
     <row r="3837" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3837" s="4"/>
-      <c r="B3837" s="36" t="s">
+      <c r="B3837" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="C3837" s="37"/>
+      <c r="C3837" s="39"/>
     </row>
     <row r="3838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3838" s="12" t="s">
@@ -24590,7 +24590,7 @@
       <c r="A3851" s="8">
         <v>5.2</v>
       </c>
-      <c r="B3851" s="38" t="s">
+      <c r="B3851" s="37" t="s">
         <v>584</v>
       </c>
       <c r="C3851" s="14" t="s">
@@ -24599,12 +24599,12 @@
     </row>
     <row r="3852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3852" s="8"/>
-      <c r="B3852" s="38"/>
+      <c r="B3852" s="37"/>
       <c r="C3852" s="14"/>
     </row>
     <row r="3853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3853" s="8"/>
-      <c r="B3853" s="38"/>
+      <c r="B3853" s="37"/>
       <c r="C3853" s="14"/>
     </row>
     <row r="3854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24670,10 +24670,10 @@
     </row>
     <row r="3896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3896" s="4"/>
-      <c r="B3896" s="36" t="s">
+      <c r="B3896" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="C3896" s="37"/>
+      <c r="C3896" s="39"/>
     </row>
     <row r="3897" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3897" s="12" t="s">
@@ -24878,10 +24878,10 @@
     </row>
     <row r="4014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4014" s="4"/>
-      <c r="B4014" s="36" t="s">
+      <c r="B4014" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="C4014" s="37"/>
+      <c r="C4014" s="39"/>
     </row>
     <row r="4015" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4015" s="12" t="s">
@@ -24988,14 +24988,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4025" s="9"/>
-      <c r="C4025" s="39" t="s">
+      <c r="C4025" s="36" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="4026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4026" s="8"/>
       <c r="B4026" s="9"/>
-      <c r="C4026" s="39"/>
+      <c r="C4026" s="36"/>
     </row>
     <row r="4027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4027" s="8">
@@ -25179,10 +25179,10 @@
     </row>
     <row r="4132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4132" s="4"/>
-      <c r="B4132" s="36" t="s">
+      <c r="B4132" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C4132" s="37"/>
+      <c r="C4132" s="39"/>
     </row>
     <row r="4133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4133" s="12" t="s">
@@ -25285,14 +25285,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4143" s="9"/>
-      <c r="C4143" s="39" t="s">
+      <c r="C4143" s="36" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="4144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4144" s="8"/>
       <c r="B4144" s="9"/>
-      <c r="C4144" s="39"/>
+      <c r="C4144" s="36"/>
     </row>
     <row r="4145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4145" s="18">
@@ -25343,10 +25343,10 @@
     </row>
     <row r="4191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4191" s="4"/>
-      <c r="B4191" s="36" t="s">
+      <c r="B4191" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="C4191" s="37"/>
+      <c r="C4191" s="39"/>
     </row>
     <row r="4192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4192" s="12" t="s">
@@ -26130,10 +26130,10 @@
     </row>
     <row r="4604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4604" s="4"/>
-      <c r="B4604" s="36" t="s">
+      <c r="B4604" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C4604" s="37"/>
+      <c r="C4604" s="39"/>
     </row>
     <row r="4605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4605" s="12" t="s">
@@ -26240,14 +26240,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4615" s="9"/>
-      <c r="C4615" s="39" t="s">
+      <c r="C4615" s="36" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="4616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4616" s="8"/>
       <c r="B4616" s="9"/>
-      <c r="C4616" s="39"/>
+      <c r="C4616" s="36"/>
     </row>
     <row r="4617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4617" s="18">
@@ -26298,10 +26298,10 @@
     </row>
     <row r="4663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4663" s="4"/>
-      <c r="B4663" s="36" t="s">
+      <c r="B4663" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="C4663" s="37"/>
+      <c r="C4663" s="39"/>
     </row>
     <row r="4664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4664" s="12" t="s">
@@ -26488,14 +26488,14 @@
       <c r="B4726" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C4726" s="39" t="s">
+      <c r="C4726" s="36" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="4727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4727" s="8"/>
       <c r="B4727" s="9"/>
-      <c r="C4727" s="39"/>
+      <c r="C4727" s="36"/>
     </row>
     <row r="4728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4728" s="8">
@@ -26571,10 +26571,10 @@
     </row>
     <row r="4781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4781" s="4"/>
-      <c r="B4781" s="36" t="s">
+      <c r="B4781" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C4781" s="37"/>
+      <c r="C4781" s="39"/>
     </row>
     <row r="4782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4782" s="12" t="s">
@@ -26926,10 +26926,10 @@
     </row>
     <row r="4899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4899" s="4"/>
-      <c r="B4899" s="36" t="s">
+      <c r="B4899" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="C4899" s="37"/>
+      <c r="C4899" s="39"/>
     </row>
     <row r="4900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4900" s="12" t="s">
@@ -27223,14 +27223,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B4969" s="9"/>
-      <c r="C4969" s="39" t="s">
+      <c r="C4969" s="36" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="4970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4970" s="8"/>
       <c r="B4970" s="9"/>
-      <c r="C4970" s="39"/>
+      <c r="C4970" s="36"/>
     </row>
     <row r="4971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4971" s="8">
@@ -27359,14 +27359,14 @@
         <v>3.1</v>
       </c>
       <c r="B5024" s="9"/>
-      <c r="C5024" s="39" t="s">
+      <c r="C5024" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="5025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5025" s="8"/>
       <c r="B5025" s="9"/>
-      <c r="C5025" s="39"/>
+      <c r="C5025" s="36"/>
     </row>
     <row r="5026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5026" s="15">
@@ -27433,10 +27433,10 @@
     </row>
     <row r="5076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5076" s="4"/>
-      <c r="B5076" s="36" t="s">
+      <c r="B5076" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="C5076" s="37"/>
+      <c r="C5076" s="39"/>
     </row>
     <row r="5077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5077" s="12" t="s">
@@ -27501,14 +27501,14 @@
         <v>3.1</v>
       </c>
       <c r="B5083" s="9"/>
-      <c r="C5083" s="39" t="s">
+      <c r="C5083" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="5084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5084" s="8"/>
       <c r="B5084" s="9"/>
-      <c r="C5084" s="39"/>
+      <c r="C5084" s="36"/>
     </row>
     <row r="5085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5085" s="15">
@@ -27558,14 +27558,14 @@
         <v>6.1</v>
       </c>
       <c r="B5090" s="9"/>
-      <c r="C5090" s="39" t="s">
+      <c r="C5090" s="36" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="5091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5091" s="8"/>
       <c r="B5091" s="9"/>
-      <c r="C5091" s="39"/>
+      <c r="C5091" s="36"/>
     </row>
     <row r="5092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5092" s="18">
@@ -27616,10 +27616,10 @@
     </row>
     <row r="5135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5135" s="4"/>
-      <c r="B5135" s="36" t="s">
+      <c r="B5135" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C5135" s="37"/>
+      <c r="C5135" s="39"/>
     </row>
     <row r="5136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5136" s="12" t="s">
@@ -27710,7 +27710,7 @@
       <c r="A5145" s="8">
         <v>4.2</v>
       </c>
-      <c r="B5145" s="38" t="s">
+      <c r="B5145" s="37" t="s">
         <v>156</v>
       </c>
       <c r="C5145" s="10" t="s">
@@ -27719,12 +27719,12 @@
     </row>
     <row r="5146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5146" s="8"/>
-      <c r="B5146" s="38"/>
+      <c r="B5146" s="37"/>
       <c r="C5146" s="10"/>
     </row>
     <row r="5147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5147" s="8"/>
-      <c r="B5147" s="38"/>
+      <c r="B5147" s="37"/>
       <c r="C5147" s="10"/>
     </row>
     <row r="5148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27738,7 +27738,7 @@
       <c r="A5149" s="8">
         <v>5.2</v>
       </c>
-      <c r="B5149" s="38" t="s">
+      <c r="B5149" s="37" t="s">
         <v>157</v>
       </c>
       <c r="C5149" s="10" t="s">
@@ -27747,12 +27747,12 @@
     </row>
     <row r="5150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5150" s="8"/>
-      <c r="B5150" s="38"/>
+      <c r="B5150" s="37"/>
       <c r="C5150" s="10"/>
     </row>
     <row r="5151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5151" s="8"/>
-      <c r="B5151" s="38"/>
+      <c r="B5151" s="37"/>
       <c r="C5151" s="10"/>
     </row>
     <row r="5152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28273,10 +28273,10 @@
     </row>
     <row r="5430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5430" s="4"/>
-      <c r="B5430" s="36" t="s">
+      <c r="B5430" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="C5430" s="37"/>
+      <c r="C5430" s="39"/>
     </row>
     <row r="5431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5431" s="12" t="s">
@@ -28400,10 +28400,10 @@
     </row>
     <row r="5489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5489" s="4"/>
-      <c r="B5489" s="36" t="s">
+      <c r="B5489" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="C5489" s="37"/>
+      <c r="C5489" s="39"/>
     </row>
     <row r="5490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5490" s="12" t="s">
@@ -28562,10 +28562,10 @@
     </row>
     <row r="5548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5548" s="4"/>
-      <c r="B5548" s="36" t="s">
+      <c r="B5548" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="C5548" s="37"/>
+      <c r="C5548" s="39"/>
     </row>
     <row r="5549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5549" s="12" t="s">
@@ -28700,14 +28700,14 @@
         <v>6.1</v>
       </c>
       <c r="B5563" s="9"/>
-      <c r="C5563" s="39" t="s">
+      <c r="C5563" s="36" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="5564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5564" s="8"/>
       <c r="B5564" s="9"/>
-      <c r="C5564" s="39"/>
+      <c r="C5564" s="36"/>
     </row>
     <row r="5565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5565" s="18">
@@ -28758,10 +28758,10 @@
     </row>
     <row r="5607" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5607" s="4"/>
-      <c r="B5607" s="36" t="s">
+      <c r="B5607" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="C5607" s="37"/>
+      <c r="C5607" s="39"/>
     </row>
     <row r="5608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5608" s="12" t="s">
@@ -29068,10 +29068,10 @@
     </row>
     <row r="5725" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5725" s="4"/>
-      <c r="B5725" s="36" t="s">
+      <c r="B5725" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="C5725" s="37"/>
+      <c r="C5725" s="39"/>
     </row>
     <row r="5726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5726" s="12" t="s">
@@ -29192,7 +29192,7 @@
       <c r="A5739" s="8">
         <v>5.2</v>
       </c>
-      <c r="B5739" s="38" t="s">
+      <c r="B5739" s="37" t="s">
         <v>584</v>
       </c>
       <c r="C5739" s="10" t="s">
@@ -29201,12 +29201,12 @@
     </row>
     <row r="5740" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5740" s="8"/>
-      <c r="B5740" s="38"/>
+      <c r="B5740" s="37"/>
       <c r="C5740" s="10"/>
     </row>
     <row r="5741" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5741" s="8"/>
-      <c r="B5741" s="38"/>
+      <c r="B5741" s="37"/>
       <c r="C5741" s="10"/>
     </row>
     <row r="5742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -29370,10 +29370,10 @@
     </row>
     <row r="5784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5784" s="4"/>
-      <c r="B5784" s="36" t="s">
+      <c r="B5784" s="38" t="s">
         <v>343</v>
       </c>
-      <c r="C5784" s="37"/>
+      <c r="C5784" s="39"/>
     </row>
     <row r="5785" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5785" s="12" t="s">
@@ -30090,10 +30090,10 @@
     </row>
     <row r="6020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6020" s="4"/>
-      <c r="B6020" s="36" t="s">
+      <c r="B6020" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="C6020" s="37"/>
+      <c r="C6020" s="39"/>
     </row>
     <row r="6021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6021" s="12" t="s">
@@ -30196,14 +30196,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6031" s="9"/>
-      <c r="C6031" s="39" t="s">
+      <c r="C6031" s="36" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="6032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6032" s="8"/>
       <c r="B6032" s="9"/>
-      <c r="C6032" s="39"/>
+      <c r="C6032" s="36"/>
     </row>
     <row r="6033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6033" s="18">
@@ -31439,10 +31439,10 @@
     </row>
     <row r="6492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6492" s="4"/>
-      <c r="B6492" s="36" t="s">
+      <c r="B6492" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C6492" s="37"/>
+      <c r="C6492" s="39"/>
     </row>
     <row r="6493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6493" s="12" t="s">
@@ -31549,14 +31549,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B6503" s="9"/>
-      <c r="C6503" s="39" t="s">
+      <c r="C6503" s="36" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="6504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6504" s="8"/>
       <c r="B6504" s="9"/>
-      <c r="C6504" s="39"/>
+      <c r="C6504" s="36"/>
     </row>
     <row r="6505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6505" s="18">
@@ -31895,14 +31895,14 @@
       <c r="B6614" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C6614" s="39" t="s">
+      <c r="C6614" s="36" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="6615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6615" s="8"/>
       <c r="B6615" s="9"/>
-      <c r="C6615" s="39"/>
+      <c r="C6615" s="36"/>
     </row>
     <row r="6616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6616" s="8">
@@ -31978,10 +31978,10 @@
     </row>
     <row r="6669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6669" s="4"/>
-      <c r="B6669" s="36" t="s">
+      <c r="B6669" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C6669" s="37"/>
+      <c r="C6669" s="39"/>
     </row>
     <row r="6670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6670" s="12" t="s">
@@ -32536,10 +32536,10 @@
     </row>
     <row r="6787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6787" s="4"/>
-      <c r="B6787" s="36" t="s">
+      <c r="B6787" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="C6787" s="37"/>
+      <c r="C6787" s="39"/>
     </row>
     <row r="6788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6788" s="12" t="s">
@@ -32889,14 +32889,14 @@
         <v>3.1</v>
       </c>
       <c r="B6853" s="9"/>
-      <c r="C6853" s="39" t="s">
+      <c r="C6853" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="6854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6854" s="8"/>
       <c r="B6854" s="9"/>
-      <c r="C6854" s="39"/>
+      <c r="C6854" s="36"/>
     </row>
     <row r="6855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6855" s="8">
@@ -33029,14 +33029,14 @@
         <v>3.1</v>
       </c>
       <c r="B6912" s="9"/>
-      <c r="C6912" s="39" t="s">
+      <c r="C6912" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="6913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6913" s="8"/>
       <c r="B6913" s="9"/>
-      <c r="C6913" s="39"/>
+      <c r="C6913" s="36"/>
     </row>
     <row r="6914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6914" s="8">
@@ -33201,10 +33201,10 @@
     </row>
     <row r="6964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6964" s="4"/>
-      <c r="B6964" s="36" t="s">
+      <c r="B6964" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="C6964" s="37"/>
+      <c r="C6964" s="39"/>
     </row>
     <row r="6965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6965" s="12" t="s">
@@ -33269,14 +33269,14 @@
         <v>3.1</v>
       </c>
       <c r="B6971" s="9"/>
-      <c r="C6971" s="39" t="s">
+      <c r="C6971" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="6972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6972" s="8"/>
       <c r="B6972" s="9"/>
-      <c r="C6972" s="39"/>
+      <c r="C6972" s="36"/>
     </row>
     <row r="6973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6973" s="8">
@@ -33326,14 +33326,14 @@
         <v>6.1</v>
       </c>
       <c r="B6978" s="9"/>
-      <c r="C6978" s="39" t="s">
+      <c r="C6978" s="36" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="6979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6979" s="8"/>
       <c r="B6979" s="9"/>
-      <c r="C6979" s="39"/>
+      <c r="C6979" s="36"/>
     </row>
     <row r="6980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6980" s="18">
@@ -33384,10 +33384,10 @@
     </row>
     <row r="7023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7023" s="4"/>
-      <c r="B7023" s="36" t="s">
+      <c r="B7023" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C7023" s="37"/>
+      <c r="C7023" s="39"/>
     </row>
     <row r="7024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7024" s="12" t="s">
@@ -33478,7 +33478,7 @@
       <c r="A7033" s="8">
         <v>4.2</v>
       </c>
-      <c r="B7033" s="38" t="s">
+      <c r="B7033" s="37" t="s">
         <v>156</v>
       </c>
       <c r="C7033" s="10" t="s">
@@ -33487,12 +33487,12 @@
     </row>
     <row r="7034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7034" s="8"/>
-      <c r="B7034" s="38"/>
+      <c r="B7034" s="37"/>
       <c r="C7034" s="10"/>
     </row>
     <row r="7035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7035" s="8"/>
-      <c r="B7035" s="38"/>
+      <c r="B7035" s="37"/>
       <c r="C7035" s="10"/>
     </row>
     <row r="7036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33506,7 +33506,7 @@
       <c r="A7037" s="8">
         <v>5.2</v>
       </c>
-      <c r="B7037" s="38" t="s">
+      <c r="B7037" s="37" t="s">
         <v>157</v>
       </c>
       <c r="C7037" s="10" t="s">
@@ -33515,12 +33515,12 @@
     </row>
     <row r="7038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7038" s="8"/>
-      <c r="B7038" s="38"/>
+      <c r="B7038" s="37"/>
       <c r="C7038" s="10"/>
     </row>
     <row r="7039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7039" s="8"/>
-      <c r="B7039" s="38"/>
+      <c r="B7039" s="37"/>
       <c r="C7039" s="10"/>
     </row>
     <row r="7040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34130,19 +34130,19 @@
       <c r="A7209" s="8">
         <v>4.0999999999999996</v>
       </c>
-      <c r="B7209" s="38" t="s">
+      <c r="B7209" s="37" t="s">
         <v>327</v>
       </c>
       <c r="C7209" s="10"/>
     </row>
     <row r="7210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7210" s="8"/>
-      <c r="B7210" s="38"/>
+      <c r="B7210" s="37"/>
       <c r="C7210" s="10"/>
     </row>
     <row r="7211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7211" s="8"/>
-      <c r="B7211" s="38"/>
+      <c r="B7211" s="37"/>
       <c r="C7211" s="10"/>
     </row>
     <row r="7212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34263,10 +34263,10 @@
     </row>
     <row r="7318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7318" s="4"/>
-      <c r="B7318" s="36" t="s">
+      <c r="B7318" s="38" t="s">
         <v>498</v>
       </c>
-      <c r="C7318" s="37"/>
+      <c r="C7318" s="39"/>
     </row>
     <row r="7319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7319" s="12" t="s">
@@ -34689,10 +34689,10 @@
     </row>
     <row r="7436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7436" s="4"/>
-      <c r="B7436" s="36" t="s">
+      <c r="B7436" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="C7436" s="37"/>
+      <c r="C7436" s="39"/>
     </row>
     <row r="7437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7437" s="12" t="s">
@@ -34827,14 +34827,14 @@
         <v>6.1</v>
       </c>
       <c r="B7451" s="27"/>
-      <c r="C7451" s="39" t="s">
+      <c r="C7451" s="36" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="7452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7452" s="8"/>
       <c r="B7452" s="27"/>
-      <c r="C7452" s="39"/>
+      <c r="C7452" s="36"/>
     </row>
     <row r="7453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7453" s="18">
@@ -35187,14 +35187,14 @@
       <c r="B7558" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C7558" s="39" t="s">
+      <c r="C7558" s="36" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="7559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7559" s="18"/>
       <c r="B7559" s="9"/>
-      <c r="C7559" s="39"/>
+      <c r="C7559" s="36"/>
     </row>
     <row r="7560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7560" s="8">
@@ -35270,10 +35270,10 @@
     </row>
     <row r="7613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7613" s="4"/>
-      <c r="B7613" s="36" t="s">
+      <c r="B7613" s="38" t="s">
         <v>339</v>
       </c>
-      <c r="C7613" s="37"/>
+      <c r="C7613" s="39"/>
     </row>
     <row r="7614" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7614" s="12" t="s">
@@ -35394,7 +35394,7 @@
       <c r="A7627" s="8">
         <v>5.2</v>
       </c>
-      <c r="B7627" s="38" t="s">
+      <c r="B7627" s="37" t="s">
         <v>584</v>
       </c>
       <c r="C7627" s="10" t="s">
@@ -35403,12 +35403,12 @@
     </row>
     <row r="7628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7628" s="8"/>
-      <c r="B7628" s="38"/>
+      <c r="B7628" s="37"/>
       <c r="C7628" s="10"/>
     </row>
     <row r="7629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7629" s="8"/>
-      <c r="B7629" s="38"/>
+      <c r="B7629" s="37"/>
       <c r="C7629" s="10"/>
     </row>
     <row r="7630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35474,10 +35474,10 @@
     </row>
     <row r="7672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7672" s="4"/>
-      <c r="B7672" s="36" t="s">
+      <c r="B7672" s="38" t="s">
         <v>343</v>
       </c>
-      <c r="C7672" s="37"/>
+      <c r="C7672" s="39"/>
     </row>
     <row r="7673" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7673" s="12" t="s">
@@ -37183,14 +37183,14 @@
       <c r="B8502" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C8502" s="39" t="s">
+      <c r="C8502" s="36" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="8503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8503" s="8"/>
       <c r="B8503" s="9"/>
-      <c r="C8503" s="39"/>
+      <c r="C8503" s="36"/>
     </row>
     <row r="8504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8504" s="8">
@@ -37266,10 +37266,10 @@
     </row>
     <row r="8557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8557" s="4"/>
-      <c r="B8557" s="36" t="s">
+      <c r="B8557" s="38" t="s">
         <v>376</v>
       </c>
-      <c r="C8557" s="37"/>
+      <c r="C8557" s="39"/>
     </row>
     <row r="8558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8558" s="12" t="s">
@@ -37614,10 +37614,10 @@
     </row>
     <row r="8675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8675" s="4"/>
-      <c r="B8675" s="36" t="s">
+      <c r="B8675" s="38" t="s">
         <v>380</v>
       </c>
-      <c r="C8675" s="37"/>
+      <c r="C8675" s="39"/>
     </row>
     <row r="8676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8676" s="12" t="s">
@@ -37869,14 +37869,14 @@
         <v>3.1</v>
       </c>
       <c r="B8741" s="9"/>
-      <c r="C8741" s="39" t="s">
+      <c r="C8741" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="8742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8742" s="8"/>
       <c r="B8742" s="9"/>
-      <c r="C8742" s="39"/>
+      <c r="C8742" s="36"/>
     </row>
     <row r="8743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8743" s="15">
@@ -38009,14 +38009,14 @@
         <v>3.1</v>
       </c>
       <c r="B8800" s="9"/>
-      <c r="C8800" s="39" t="s">
+      <c r="C8800" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="8801" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8801" s="8"/>
       <c r="B8801" s="9"/>
-      <c r="C8801" s="39"/>
+      <c r="C8801" s="36"/>
     </row>
     <row r="8802" spans="1:3" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8802" s="15">
@@ -38149,14 +38149,14 @@
         <v>3.1</v>
       </c>
       <c r="B8859" s="9"/>
-      <c r="C8859" s="39" t="s">
+      <c r="C8859" s="36" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="8860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8860" s="8"/>
       <c r="B8860" s="9"/>
-      <c r="C8860" s="39"/>
+      <c r="C8860" s="36"/>
     </row>
     <row r="8861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8861" s="15">
@@ -38221,10 +38221,10 @@
     </row>
     <row r="8911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8911" s="4"/>
-      <c r="B8911" s="36" t="s">
+      <c r="B8911" s="38" t="s">
         <v>386</v>
       </c>
-      <c r="C8911" s="37"/>
+      <c r="C8911" s="39"/>
     </row>
     <row r="8912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8912" s="12" t="s">
@@ -38315,7 +38315,7 @@
       <c r="A8921" s="8">
         <v>4.2</v>
       </c>
-      <c r="B8921" s="38" t="s">
+      <c r="B8921" s="37" t="s">
         <v>156</v>
       </c>
       <c r="C8921" s="14" t="s">
@@ -38324,12 +38324,12 @@
     </row>
     <row r="8922" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8922" s="8"/>
-      <c r="B8922" s="38"/>
+      <c r="B8922" s="37"/>
       <c r="C8922" s="14"/>
     </row>
     <row r="8923" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8923" s="8"/>
-      <c r="B8923" s="38"/>
+      <c r="B8923" s="37"/>
       <c r="C8923" s="14"/>
     </row>
     <row r="8924" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -38343,7 +38343,7 @@
       <c r="A8925" s="8">
         <v>5.2</v>
       </c>
-      <c r="B8925" s="38" t="s">
+      <c r="B8925" s="37" t="s">
         <v>157</v>
       </c>
       <c r="C8925" s="14" t="s">
@@ -38352,12 +38352,12 @@
     </row>
     <row r="8926" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8926" s="8"/>
-      <c r="B8926" s="38"/>
+      <c r="B8926" s="37"/>
       <c r="C8926" s="14"/>
     </row>
     <row r="8927" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8927" s="8"/>
-      <c r="B8927" s="38"/>
+      <c r="B8927" s="37"/>
       <c r="C8927" s="14"/>
     </row>
     <row r="8928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -39529,10 +39529,10 @@
     </row>
     <row r="9501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9501" s="4"/>
-      <c r="B9501" s="36" t="s">
+      <c r="B9501" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="C9501" s="37"/>
+      <c r="C9501" s="39"/>
     </row>
     <row r="9502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9502" s="12" t="s">
@@ -39653,7 +39653,7 @@
       <c r="A9515" s="8">
         <v>5.2</v>
       </c>
-      <c r="B9515" s="38" t="s">
+      <c r="B9515" s="37" t="s">
         <v>584</v>
       </c>
       <c r="C9515" s="10" t="s">
@@ -39662,12 +39662,12 @@
     </row>
     <row r="9516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9516" s="8"/>
-      <c r="B9516" s="38"/>
+      <c r="B9516" s="37"/>
       <c r="C9516" s="10"/>
     </row>
     <row r="9517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9517" s="8"/>
-      <c r="B9517" s="38"/>
+      <c r="B9517" s="37"/>
       <c r="C9517" s="10"/>
     </row>
     <row r="9518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41436,14 +41436,14 @@
       <c r="B10390" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C10390" s="39" t="s">
+      <c r="C10390" s="36" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="10391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10391" s="8"/>
       <c r="B10391" s="9"/>
-      <c r="C10391" s="39"/>
+      <c r="C10391" s="36"/>
     </row>
     <row r="10392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10392" s="8">
@@ -41519,10 +41519,10 @@
     </row>
     <row r="10445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10445" s="4"/>
-      <c r="B10445" s="36" t="s">
+      <c r="B10445" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C10445" s="37"/>
+      <c r="C10445" s="39"/>
     </row>
     <row r="10446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10446" s="12" t="s">
@@ -41881,10 +41881,10 @@
     </row>
     <row r="10563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10563" s="4"/>
-      <c r="B10563" s="36" t="s">
+      <c r="B10563" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="C10563" s="37"/>
+      <c r="C10563" s="39"/>
     </row>
     <row r="10564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10564" s="12" t="s">
@@ -42136,14 +42136,14 @@
         <v>3.1</v>
       </c>
       <c r="B10629" s="9"/>
-      <c r="C10629" s="39" t="s">
+      <c r="C10629" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="10630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10630" s="8"/>
       <c r="B10630" s="9"/>
-      <c r="C10630" s="39"/>
+      <c r="C10630" s="36"/>
     </row>
     <row r="10631" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10631" s="15">
@@ -42278,14 +42278,14 @@
         <v>3.1</v>
       </c>
       <c r="B10688" s="9"/>
-      <c r="C10688" s="39" t="s">
+      <c r="C10688" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="10689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10689" s="8"/>
       <c r="B10689" s="9"/>
-      <c r="C10689" s="39"/>
+      <c r="C10689" s="36"/>
     </row>
     <row r="10690" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10690" s="15">
@@ -42420,14 +42420,14 @@
         <v>3.1</v>
       </c>
       <c r="B10747" s="9"/>
-      <c r="C10747" s="39" t="s">
+      <c r="C10747" s="36" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="10748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10748" s="8"/>
       <c r="B10748" s="9"/>
-      <c r="C10748" s="39"/>
+      <c r="C10748" s="36"/>
     </row>
     <row r="10749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10749" s="15">
@@ -42494,10 +42494,10 @@
     </row>
     <row r="10799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10799" s="4"/>
-      <c r="B10799" s="36" t="s">
+      <c r="B10799" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C10799" s="37"/>
+      <c r="C10799" s="39"/>
     </row>
     <row r="10800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10800" s="12" t="s">
@@ -42588,7 +42588,7 @@
       <c r="A10809" s="8">
         <v>4.2</v>
       </c>
-      <c r="B10809" s="38" t="s">
+      <c r="B10809" s="37" t="s">
         <v>156</v>
       </c>
       <c r="C10809" s="10" t="s">
@@ -42597,12 +42597,12 @@
     </row>
     <row r="10810" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10810" s="8"/>
-      <c r="B10810" s="38"/>
+      <c r="B10810" s="37"/>
       <c r="C10810" s="10"/>
     </row>
     <row r="10811" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10811" s="8"/>
-      <c r="B10811" s="38"/>
+      <c r="B10811" s="37"/>
       <c r="C10811" s="10"/>
     </row>
     <row r="10812" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42616,7 +42616,7 @@
       <c r="A10813" s="8">
         <v>5.2</v>
       </c>
-      <c r="B10813" s="38" t="s">
+      <c r="B10813" s="37" t="s">
         <v>157</v>
       </c>
       <c r="C10813" s="10" t="s">
@@ -42625,12 +42625,12 @@
     </row>
     <row r="10814" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10814" s="8"/>
-      <c r="B10814" s="38"/>
+      <c r="B10814" s="37"/>
       <c r="C10814" s="10"/>
     </row>
     <row r="10815" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10815" s="8"/>
-      <c r="B10815" s="38"/>
+      <c r="B10815" s="37"/>
       <c r="C10815" s="10"/>
     </row>
     <row r="10816" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43857,14 +43857,14 @@
         <v>2.1</v>
       </c>
       <c r="B11335" s="9"/>
-      <c r="C11335" s="39" t="s">
+      <c r="C11335" s="36" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="11336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11336" s="8"/>
       <c r="B11336" s="9"/>
-      <c r="C11336" s="39"/>
+      <c r="C11336" s="36"/>
     </row>
     <row r="11337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11337" s="8">
@@ -43897,10 +43897,10 @@
     </row>
     <row r="11389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11389" s="4"/>
-      <c r="B11389" s="36" t="s">
+      <c r="B11389" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="C11389" s="37"/>
+      <c r="C11389" s="39"/>
     </row>
     <row r="11390" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11390" s="12" t="s">
@@ -44021,7 +44021,7 @@
       <c r="A11403" s="8">
         <v>5.2</v>
       </c>
-      <c r="B11403" s="38" t="s">
+      <c r="B11403" s="37" t="s">
         <v>584</v>
       </c>
       <c r="C11403" s="10" t="s">
@@ -44030,12 +44030,12 @@
     </row>
     <row r="11404" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11404" s="8"/>
-      <c r="B11404" s="38"/>
+      <c r="B11404" s="37"/>
       <c r="C11404" s="10"/>
     </row>
     <row r="11405" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11405" s="8"/>
-      <c r="B11405" s="38"/>
+      <c r="B11405" s="37"/>
       <c r="C11405" s="10"/>
     </row>
     <row r="11406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44061,14 +44061,14 @@
         <v>7.1</v>
       </c>
       <c r="B11408" s="9"/>
-      <c r="C11408" s="39" t="s">
+      <c r="C11408" s="36" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="11409" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11409" s="8"/>
       <c r="B11409" s="9"/>
-      <c r="C11409" s="39"/>
+      <c r="C11409" s="36"/>
     </row>
     <row r="11410" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11410" s="8">
@@ -44295,14 +44295,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B11516" s="9"/>
-      <c r="C11516" s="39" t="s">
+      <c r="C11516" s="36" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="11517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11517" s="8"/>
       <c r="B11517" s="9"/>
-      <c r="C11517" s="39"/>
+      <c r="C11517" s="36"/>
     </row>
     <row r="11518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11518" s="8">
@@ -44423,14 +44423,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B11575" s="9"/>
-      <c r="C11575" s="39" t="s">
+      <c r="C11575" s="36" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="11576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11576" s="8"/>
       <c r="B11576" s="9"/>
-      <c r="C11576" s="39"/>
+      <c r="C11576" s="36"/>
     </row>
     <row r="11577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11577" s="8">
@@ -44551,14 +44551,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B11634" s="9"/>
-      <c r="C11634" s="39" t="s">
+      <c r="C11634" s="36" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="11635" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11635" s="8"/>
       <c r="B11635" s="9"/>
-      <c r="C11635" s="39"/>
+      <c r="C11635" s="36"/>
     </row>
     <row r="11636" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11636" s="8">
@@ -44892,14 +44892,14 @@
         <v>7.1</v>
       </c>
       <c r="B11758" s="9"/>
-      <c r="C11758" s="39" t="s">
+      <c r="C11758" s="36" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="11759" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11759" s="8"/>
       <c r="B11759" s="9"/>
-      <c r="C11759" s="39"/>
+      <c r="C11759" s="36"/>
     </row>
     <row r="11760" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11760" s="8">
@@ -45071,14 +45071,14 @@
         <v>2.1</v>
       </c>
       <c r="B11866" s="9"/>
-      <c r="C11866" s="39" t="s">
+      <c r="C11866" s="36" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="11867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11867" s="8"/>
       <c r="B11867" s="9"/>
-      <c r="C11867" s="39"/>
+      <c r="C11867" s="36"/>
     </row>
     <row r="11868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11868" s="8">
@@ -45380,14 +45380,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B12047" s="9"/>
-      <c r="C12047" s="39" t="s">
+      <c r="C12047" s="36" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="12048" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12048" s="8"/>
       <c r="B12048" s="9"/>
-      <c r="C12048" s="39"/>
+      <c r="C12048" s="36"/>
     </row>
     <row r="12049" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12049" s="8">
@@ -45512,14 +45512,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B12106" s="9"/>
-      <c r="C12106" s="39" t="s">
+      <c r="C12106" s="36" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12107" s="8"/>
       <c r="B12107" s="9"/>
-      <c r="C12107" s="39"/>
+      <c r="C12107" s="36"/>
     </row>
     <row r="12108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12108" s="8">
@@ -45552,10 +45552,10 @@
     </row>
     <row r="12156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12156" s="4"/>
-      <c r="B12156" s="36" t="s">
+      <c r="B12156" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C12156" s="37"/>
+      <c r="C12156" s="39"/>
     </row>
     <row r="12157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12157" s="12" t="s">
@@ -45827,14 +45827,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12226" s="9"/>
-      <c r="C12226" s="39" t="s">
+      <c r="C12226" s="36" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12227" s="8"/>
       <c r="B12227" s="9"/>
-      <c r="C12227" s="39"/>
+      <c r="C12227" s="36"/>
     </row>
     <row r="12228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12228" s="8">
@@ -45910,14 +45910,14 @@
       <c r="B12278" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C12278" s="39" t="s">
+      <c r="C12278" s="36" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="12279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12279" s="8"/>
       <c r="B12279" s="9"/>
-      <c r="C12279" s="39"/>
+      <c r="C12279" s="36"/>
     </row>
     <row r="12280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12280" s="8">
@@ -45993,10 +45993,10 @@
     </row>
     <row r="12333" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12333" s="4"/>
-      <c r="B12333" s="36" t="s">
+      <c r="B12333" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C12333" s="37"/>
+      <c r="C12333" s="39"/>
     </row>
     <row r="12334" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12334" s="12" t="s">
@@ -46161,14 +46161,14 @@
         <v>7.1</v>
       </c>
       <c r="B12352" s="9"/>
-      <c r="C12352" s="39" t="s">
+      <c r="C12352" s="36" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12353" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12353" s="8"/>
       <c r="B12353" s="9"/>
-      <c r="C12353" s="39"/>
+      <c r="C12353" s="36"/>
     </row>
     <row r="12354" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12354" s="8">
@@ -46325,14 +46325,14 @@
         <v>6.1</v>
       </c>
       <c r="B12405" s="9"/>
-      <c r="C12405" s="39" t="s">
+      <c r="C12405" s="36" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12406" s="8"/>
       <c r="B12406" s="9"/>
-      <c r="C12406" s="39"/>
+      <c r="C12406" s="36"/>
     </row>
     <row r="12407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12407" s="8">
@@ -46365,10 +46365,10 @@
     </row>
     <row r="12451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12451" s="4"/>
-      <c r="B12451" s="36" t="s">
+      <c r="B12451" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="C12451" s="37"/>
+      <c r="C12451" s="39"/>
     </row>
     <row r="12452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12452" s="12" t="s">
@@ -46517,14 +46517,14 @@
         <v>7.1</v>
       </c>
       <c r="B12468" s="9"/>
-      <c r="C12468" s="39" t="s">
+      <c r="C12468" s="36" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12469" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12469" s="8"/>
       <c r="B12469" s="9"/>
-      <c r="C12469" s="39"/>
+      <c r="C12469" s="36"/>
     </row>
     <row r="12470" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12470" s="8">
@@ -46557,10 +46557,10 @@
     </row>
     <row r="12510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12510" s="4"/>
-      <c r="B12510" s="36" t="s">
+      <c r="B12510" s="38" t="s">
         <v>505</v>
       </c>
-      <c r="C12510" s="37"/>
+      <c r="C12510" s="39"/>
     </row>
     <row r="12511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12511" s="12" t="s">
@@ -46651,7 +46651,7 @@
       <c r="A12520" s="8">
         <v>4.2</v>
       </c>
-      <c r="B12520" s="38" t="s">
+      <c r="B12520" s="37" t="s">
         <v>506</v>
       </c>
       <c r="C12520" s="10" t="s">
@@ -46660,12 +46660,12 @@
     </row>
     <row r="12521" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12521" s="8"/>
-      <c r="B12521" s="38"/>
+      <c r="B12521" s="37"/>
       <c r="C12521" s="10"/>
     </row>
     <row r="12522" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12522" s="8"/>
-      <c r="B12522" s="38"/>
+      <c r="B12522" s="37"/>
       <c r="C12522" s="10"/>
     </row>
     <row r="12523" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -46812,14 +46812,14 @@
         <v>3.1</v>
       </c>
       <c r="B12576" s="9"/>
-      <c r="C12576" s="39" t="s">
+      <c r="C12576" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="12577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12577" s="8"/>
       <c r="B12577" s="9"/>
-      <c r="C12577" s="39"/>
+      <c r="C12577" s="36"/>
     </row>
     <row r="12578" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12578" s="8">
@@ -46851,14 +46851,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12581" s="27"/>
-      <c r="C12581" s="39" t="s">
+      <c r="C12581" s="36" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12582" s="8"/>
       <c r="B12582" s="27"/>
-      <c r="C12582" s="39"/>
+      <c r="C12582" s="36"/>
     </row>
     <row r="12583" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12583" s="8">
@@ -46891,10 +46891,10 @@
     </row>
     <row r="12628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12628" s="4"/>
-      <c r="B12628" s="36" t="s">
+      <c r="B12628" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="C12628" s="37"/>
+      <c r="C12628" s="39"/>
     </row>
     <row r="12629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12629" s="12" t="s">
@@ -46959,28 +46959,28 @@
         <v>3.1</v>
       </c>
       <c r="B12635" s="9"/>
-      <c r="C12635" s="39" t="s">
+      <c r="C12635" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="12636" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12636" s="8"/>
       <c r="B12636" s="9"/>
-      <c r="C12636" s="39"/>
+      <c r="C12636" s="36"/>
     </row>
     <row r="12637" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12637" s="8">
+      <c r="A12637" s="15">
         <v>3.2</v>
       </c>
-      <c r="B12637" s="9"/>
-      <c r="C12637" s="10"/>
+      <c r="B12637" s="16"/>
+      <c r="C12637" s="23"/>
     </row>
     <row r="12638" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12638" s="8">
+      <c r="A12638" s="15">
         <v>4.0999999999999996</v>
       </c>
-      <c r="B12638" s="9"/>
-      <c r="C12638" s="10"/>
+      <c r="B12638" s="16"/>
+      <c r="C12638" s="23"/>
     </row>
     <row r="12639" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12639" s="8">
@@ -47069,10 +47069,10 @@
     </row>
     <row r="12687" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12687" s="4"/>
-      <c r="B12687" s="36" t="s">
+      <c r="B12687" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C12687" s="37"/>
+      <c r="C12687" s="39"/>
     </row>
     <row r="12688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12688" s="12" t="s">
@@ -47163,7 +47163,7 @@
       <c r="A12697" s="8">
         <v>4.2</v>
       </c>
-      <c r="B12697" s="38" t="s">
+      <c r="B12697" s="37" t="s">
         <v>156</v>
       </c>
       <c r="C12697" s="10" t="s">
@@ -47172,12 +47172,12 @@
     </row>
     <row r="12698" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12698" s="8"/>
-      <c r="B12698" s="38"/>
+      <c r="B12698" s="37"/>
       <c r="C12698" s="10"/>
     </row>
     <row r="12699" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12699" s="8"/>
-      <c r="B12699" s="38"/>
+      <c r="B12699" s="37"/>
       <c r="C12699" s="10"/>
     </row>
     <row r="12700" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47191,7 +47191,7 @@
       <c r="A12701" s="8">
         <v>5.2</v>
       </c>
-      <c r="B12701" s="38" t="s">
+      <c r="B12701" s="37" t="s">
         <v>157</v>
       </c>
       <c r="C12701" s="10" t="s">
@@ -47200,12 +47200,12 @@
     </row>
     <row r="12702" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12702" s="8"/>
-      <c r="B12702" s="38"/>
+      <c r="B12702" s="37"/>
       <c r="C12702" s="10"/>
     </row>
     <row r="12703" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12703" s="8"/>
-      <c r="B12703" s="38"/>
+      <c r="B12703" s="37"/>
       <c r="C12703" s="10"/>
     </row>
     <row r="12704" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -47247,14 +47247,14 @@
         <v>7.1</v>
       </c>
       <c r="B12708" s="9"/>
-      <c r="C12708" s="39" t="s">
+      <c r="C12708" s="36" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12709" s="8"/>
       <c r="B12709" s="9"/>
-      <c r="C12709" s="39"/>
+      <c r="C12709" s="36"/>
     </row>
     <row r="12710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12710" s="8">
@@ -47508,14 +47508,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B12820" s="27"/>
-      <c r="C12820" s="39" t="s">
+      <c r="C12820" s="36" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="12821" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12821" s="8"/>
       <c r="B12821" s="27"/>
-      <c r="C12821" s="39"/>
+      <c r="C12821" s="36"/>
     </row>
     <row r="12822" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12822" s="8">
@@ -47742,10 +47742,10 @@
     </row>
     <row r="12982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12982" s="4"/>
-      <c r="B12982" s="36" t="s">
+      <c r="B12982" s="38" t="s">
         <v>520</v>
       </c>
-      <c r="C12982" s="37"/>
+      <c r="C12982" s="39"/>
     </row>
     <row r="12983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12983" s="12" t="s">
@@ -47858,7 +47858,7 @@
       <c r="A12994" s="18">
         <v>5.2</v>
       </c>
-      <c r="B12994" s="38" t="s">
+      <c r="B12994" s="37" t="s">
         <v>521</v>
       </c>
       <c r="C12994" s="10" t="s">
@@ -47867,12 +47867,12 @@
     </row>
     <row r="12995" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12995" s="18"/>
-      <c r="B12995" s="38"/>
+      <c r="B12995" s="37"/>
       <c r="C12995" s="10"/>
     </row>
     <row r="12996" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12996" s="18"/>
-      <c r="B12996" s="38"/>
+      <c r="B12996" s="37"/>
       <c r="C12996" s="10"/>
     </row>
     <row r="12997" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48049,14 +48049,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B13056" s="9"/>
-      <c r="C13056" s="39" t="s">
+      <c r="C13056" s="36" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="13057" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13057" s="8"/>
       <c r="B13057" s="9"/>
-      <c r="C13057" s="39"/>
+      <c r="C13057" s="36"/>
     </row>
     <row r="13058" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13058" s="8">
@@ -48089,10 +48089,10 @@
     </row>
     <row r="13100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13100" s="4"/>
-      <c r="B13100" s="36" t="s">
+      <c r="B13100" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="C13100" s="37"/>
+      <c r="C13100" s="39"/>
     </row>
     <row r="13101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13101" s="12" t="s">
@@ -48406,14 +48406,14 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B13172" s="9"/>
-      <c r="C13172" s="39" t="s">
+      <c r="C13172" s="36" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="13173" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13173" s="8"/>
       <c r="B13173" s="9"/>
-      <c r="C13173" s="39"/>
+      <c r="C13173" s="36"/>
     </row>
     <row r="13174" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13174" s="8">
@@ -48498,14 +48498,14 @@
         <v>2.1</v>
       </c>
       <c r="B13223" s="9"/>
-      <c r="C13223" s="39" t="s">
+      <c r="C13223" s="36" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="13224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13224" s="8"/>
       <c r="B13224" s="9"/>
-      <c r="C13224" s="39"/>
+      <c r="C13224" s="36"/>
     </row>
     <row r="13225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13225" s="8">
@@ -48538,10 +48538,10 @@
     </row>
     <row r="13277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13277" s="4"/>
-      <c r="B13277" s="36" t="s">
+      <c r="B13277" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="C13277" s="37"/>
+      <c r="C13277" s="39"/>
     </row>
     <row r="13278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13278" s="12" t="s">
@@ -48662,7 +48662,7 @@
       <c r="A13291" s="8">
         <v>5.2</v>
       </c>
-      <c r="B13291" s="38" t="s">
+      <c r="B13291" s="37" t="s">
         <v>584</v>
       </c>
       <c r="C13291" s="10" t="s">
@@ -48671,12 +48671,12 @@
     </row>
     <row r="13292" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13292" s="8"/>
-      <c r="B13292" s="38"/>
+      <c r="B13292" s="37"/>
       <c r="C13292" s="10"/>
     </row>
     <row r="13293" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13293" s="8"/>
-      <c r="B13293" s="38"/>
+      <c r="B13293" s="37"/>
       <c r="C13293" s="10"/>
     </row>
     <row r="13294" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -48687,7 +48687,7 @@
       <c r="C13294" s="10"/>
     </row>
     <row r="13295" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13295" s="8">
+      <c r="A13295" s="18">
         <v>6.2</v>
       </c>
       <c r="B13295" s="9" t="s">
@@ -49012,7 +49012,7 @@
       <c r="C13402" s="10"/>
     </row>
     <row r="13403" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13403" s="8">
+      <c r="A13403" s="18">
         <v>3.2</v>
       </c>
       <c r="B13403" s="9" t="s">
@@ -49248,14 +49248,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B13463" s="9"/>
-      <c r="C13463" s="39" t="s">
+      <c r="C13463" s="36" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="13464" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13464" s="8"/>
       <c r="B13464" s="9"/>
-      <c r="C13464" s="39"/>
+      <c r="C13464" s="36"/>
     </row>
     <row r="13465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13465" s="8">
@@ -49668,10 +49668,10 @@
     </row>
     <row r="13631" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13631" s="4"/>
-      <c r="B13631" s="36" t="s">
+      <c r="B13631" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="C13631" s="37"/>
+      <c r="C13631" s="39"/>
     </row>
     <row r="13632" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13632" s="12" t="s">
@@ -50489,14 +50489,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B13935" s="9"/>
-      <c r="C13935" s="39" t="s">
+      <c r="C13935" s="36" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="13936" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13936" s="8"/>
       <c r="B13936" s="9"/>
-      <c r="C13936" s="39"/>
+      <c r="C13936" s="36"/>
     </row>
     <row r="13937" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13937" s="8">
@@ -50754,10 +50754,10 @@
     </row>
     <row r="14044" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14044" s="4"/>
-      <c r="B14044" s="36" t="s">
+      <c r="B14044" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C14044" s="37"/>
+      <c r="C14044" s="39"/>
     </row>
     <row r="14045" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14045" s="12" t="s">
@@ -51205,14 +51205,14 @@
       <c r="B14166" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C14166" s="39" t="s">
+      <c r="C14166" s="36" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="14167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14167" s="8"/>
       <c r="B14167" s="9"/>
-      <c r="C14167" s="39"/>
+      <c r="C14167" s="36"/>
     </row>
     <row r="14168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14168" s="8">
@@ -51288,10 +51288,10 @@
     </row>
     <row r="14221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14221" s="4"/>
-      <c r="B14221" s="36" t="s">
+      <c r="B14221" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C14221" s="37"/>
+      <c r="C14221" s="39"/>
     </row>
     <row r="14222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14222" s="12" t="s">
@@ -52276,10 +52276,10 @@
     </row>
     <row r="14457" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14457" s="4"/>
-      <c r="B14457" s="36" t="s">
+      <c r="B14457" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="C14457" s="37"/>
+      <c r="C14457" s="39"/>
     </row>
     <row r="14458" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14458" s="12" t="s">
@@ -52344,14 +52344,14 @@
         <v>3.1</v>
       </c>
       <c r="B14464" s="9"/>
-      <c r="C14464" s="39" t="s">
+      <c r="C14464" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="14465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14465" s="8"/>
       <c r="B14465" s="9"/>
-      <c r="C14465" s="39"/>
+      <c r="C14465" s="36"/>
     </row>
     <row r="14466" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14466" s="15">
@@ -52516,10 +52516,10 @@
     </row>
     <row r="14516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14516" s="4"/>
-      <c r="B14516" s="36" t="s">
+      <c r="B14516" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="C14516" s="37"/>
+      <c r="C14516" s="39"/>
     </row>
     <row r="14517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14517" s="12" t="s">
@@ -52584,28 +52584,28 @@
         <v>3.1</v>
       </c>
       <c r="B14523" s="9"/>
-      <c r="C14523" s="39" t="s">
+      <c r="C14523" s="36" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="14524" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14524" s="8"/>
       <c r="B14524" s="9"/>
-      <c r="C14524" s="39"/>
+      <c r="C14524" s="36"/>
     </row>
     <row r="14525" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14525" s="8">
+      <c r="A14525" s="15">
         <v>3.2</v>
       </c>
-      <c r="B14525" s="9"/>
-      <c r="C14525" s="10"/>
+      <c r="B14525" s="16"/>
+      <c r="C14525" s="23"/>
     </row>
     <row r="14526" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14526" s="8">
+      <c r="A14526" s="15">
         <v>4.0999999999999996</v>
       </c>
-      <c r="B14526" s="9"/>
-      <c r="C14526" s="10"/>
+      <c r="B14526" s="16"/>
+      <c r="C14526" s="23"/>
     </row>
     <row r="14527" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14527" s="8">
@@ -52694,10 +52694,10 @@
     </row>
     <row r="14575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14575" s="4"/>
-      <c r="B14575" s="36" t="s">
+      <c r="B14575" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C14575" s="37"/>
+      <c r="C14575" s="39"/>
     </row>
     <row r="14576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14576" s="12" t="s">
@@ -52788,7 +52788,7 @@
       <c r="A14585" s="8">
         <v>4.2</v>
       </c>
-      <c r="B14585" s="38" t="s">
+      <c r="B14585" s="37" t="s">
         <v>156</v>
       </c>
       <c r="C14585" s="10" t="s">
@@ -52797,12 +52797,12 @@
     </row>
     <row r="14586" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14586" s="8"/>
-      <c r="B14586" s="38"/>
+      <c r="B14586" s="37"/>
       <c r="C14586" s="10"/>
     </row>
     <row r="14587" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14587" s="8"/>
-      <c r="B14587" s="38"/>
+      <c r="B14587" s="37"/>
       <c r="C14587" s="10"/>
     </row>
     <row r="14588" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -52816,7 +52816,7 @@
       <c r="A14589" s="8">
         <v>5.2</v>
       </c>
-      <c r="B14589" s="38" t="s">
+      <c r="B14589" s="37" t="s">
         <v>157</v>
       </c>
       <c r="C14589" s="10" t="s">
@@ -52825,12 +52825,12 @@
     </row>
     <row r="14590" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14590" s="8"/>
-      <c r="B14590" s="38"/>
+      <c r="B14590" s="37"/>
       <c r="C14590" s="10"/>
     </row>
     <row r="14591" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14591" s="8"/>
-      <c r="B14591" s="38"/>
+      <c r="B14591" s="37"/>
       <c r="C14591" s="10"/>
     </row>
     <row r="14592" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -53528,14 +53528,14 @@
         <v>2.1</v>
       </c>
       <c r="B14816" s="27"/>
-      <c r="C14816" s="38" t="s">
+      <c r="C14816" s="37" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="14817" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14817" s="8"/>
       <c r="B14817" s="27"/>
-      <c r="C14817" s="38"/>
+      <c r="C14817" s="37"/>
     </row>
     <row r="14818" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14818" s="8">
@@ -53568,10 +53568,10 @@
     </row>
     <row r="14870" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14870" s="4"/>
-      <c r="B14870" s="36" t="s">
+      <c r="B14870" s="38" t="s">
         <v>577</v>
       </c>
-      <c r="C14870" s="37"/>
+      <c r="C14870" s="39"/>
     </row>
     <row r="14871" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14871" s="12" t="s">
@@ -54039,10 +54039,10 @@
     </row>
     <row r="14988" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14988" s="4"/>
-      <c r="B14988" s="36" t="s">
+      <c r="B14988" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="C14988" s="37"/>
+      <c r="C14988" s="39"/>
     </row>
     <row r="14989" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14989" s="12" t="s">
@@ -54230,10 +54230,10 @@
     </row>
     <row r="15047" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15047" s="4"/>
-      <c r="B15047" s="36" t="s">
+      <c r="B15047" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="C15047" s="37"/>
+      <c r="C15047" s="39"/>
     </row>
     <row r="15048" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15048" s="12" t="s">
@@ -54478,117 +54478,54 @@
     </row>
   </sheetData>
   <mergeCells count="182">
-    <mergeCell ref="C8741:C8742"/>
-    <mergeCell ref="B7627:B7629"/>
-    <mergeCell ref="C8502:C8503"/>
-    <mergeCell ref="B8557:C8557"/>
-    <mergeCell ref="B8675:C8675"/>
-    <mergeCell ref="B7613:C7613"/>
-    <mergeCell ref="B5784:C5784"/>
-    <mergeCell ref="B7672:C7672"/>
-    <mergeCell ref="B6020:C6020"/>
-    <mergeCell ref="C6853:C6854"/>
-    <mergeCell ref="C6912:C6913"/>
-    <mergeCell ref="C6971:C6972"/>
-    <mergeCell ref="B6964:C6964"/>
-    <mergeCell ref="C7451:C7452"/>
-    <mergeCell ref="B7436:C7436"/>
-    <mergeCell ref="C7558:C7559"/>
-    <mergeCell ref="B7209:B7211"/>
-    <mergeCell ref="B7318:C7318"/>
-    <mergeCell ref="C6978:C6979"/>
-    <mergeCell ref="B7023:C7023"/>
-    <mergeCell ref="B7033:B7035"/>
-    <mergeCell ref="B7037:B7039"/>
-    <mergeCell ref="B5607:C5607"/>
-    <mergeCell ref="B5430:C5430"/>
-    <mergeCell ref="B5489:C5489"/>
-    <mergeCell ref="B5548:C5548"/>
-    <mergeCell ref="C5563:C5564"/>
-    <mergeCell ref="B6669:C6669"/>
-    <mergeCell ref="B6787:C6787"/>
-    <mergeCell ref="C6031:C6032"/>
-    <mergeCell ref="B6492:C6492"/>
-    <mergeCell ref="C6503:C6504"/>
-    <mergeCell ref="C6614:C6615"/>
-    <mergeCell ref="B5739:B5741"/>
-    <mergeCell ref="B5725:C5725"/>
-    <mergeCell ref="C5024:C5025"/>
-    <mergeCell ref="B4781:C4781"/>
-    <mergeCell ref="C4969:C4970"/>
-    <mergeCell ref="B4899:C4899"/>
-    <mergeCell ref="C4615:C4616"/>
-    <mergeCell ref="B5135:C5135"/>
-    <mergeCell ref="B5145:B5147"/>
-    <mergeCell ref="B5149:B5151"/>
-    <mergeCell ref="B5076:C5076"/>
-    <mergeCell ref="C5083:C5084"/>
-    <mergeCell ref="C5090:C5091"/>
-    <mergeCell ref="B3365:C3365"/>
-    <mergeCell ref="C3675:C3676"/>
-    <mergeCell ref="B3257:B3259"/>
-    <mergeCell ref="B3261:B3263"/>
-    <mergeCell ref="B3247:C3247"/>
-    <mergeCell ref="B4604:C4604"/>
-    <mergeCell ref="B4663:C4663"/>
-    <mergeCell ref="C4726:C4727"/>
-    <mergeCell ref="B3660:C3660"/>
-    <mergeCell ref="B3837:C3837"/>
-    <mergeCell ref="B3896:C3896"/>
-    <mergeCell ref="C4143:C4144"/>
-    <mergeCell ref="B4191:C4191"/>
-    <mergeCell ref="B4014:C4014"/>
-    <mergeCell ref="C4025:C4026"/>
-    <mergeCell ref="B4132:C4132"/>
-    <mergeCell ref="B3851:B3853"/>
-    <mergeCell ref="B2775:C2775"/>
-    <mergeCell ref="C2838:C2839"/>
-    <mergeCell ref="B2893:C2893"/>
-    <mergeCell ref="B2657:C2657"/>
-    <mergeCell ref="B2716:C2716"/>
-    <mergeCell ref="C2727:C2728"/>
-    <mergeCell ref="C3202:C3203"/>
-    <mergeCell ref="B3188:C3188"/>
-    <mergeCell ref="C3077:C3078"/>
-    <mergeCell ref="C3136:C3137"/>
-    <mergeCell ref="C3195:C3196"/>
-    <mergeCell ref="B3011:C3011"/>
-    <mergeCell ref="C2255:C2256"/>
-    <mergeCell ref="B2244:C2244"/>
-    <mergeCell ref="B1949:C1949"/>
-    <mergeCell ref="B1890:C1890"/>
-    <mergeCell ref="B1831:C1831"/>
-    <mergeCell ref="B1772:C1772"/>
-    <mergeCell ref="B1713:C1713"/>
-    <mergeCell ref="C1787:C1788"/>
-    <mergeCell ref="B1654:C1654"/>
-    <mergeCell ref="B1963:B1965"/>
-    <mergeCell ref="B1477:C1477"/>
-    <mergeCell ref="B1359:C1359"/>
-    <mergeCell ref="B1300:C1300"/>
-    <mergeCell ref="B887:C887"/>
-    <mergeCell ref="C950:C951"/>
-    <mergeCell ref="B1064:C1064"/>
-    <mergeCell ref="C1248:C1249"/>
-    <mergeCell ref="C367:C368"/>
-    <mergeCell ref="B415:C415"/>
-    <mergeCell ref="B710:C710"/>
-    <mergeCell ref="B828:C828"/>
-    <mergeCell ref="C839:C840"/>
-    <mergeCell ref="C1307:C1308"/>
-    <mergeCell ref="C1314:C1315"/>
-    <mergeCell ref="B1369:B1371"/>
-    <mergeCell ref="B1373:B1375"/>
-    <mergeCell ref="B1123:C1123"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B1182:C1182"/>
-    <mergeCell ref="B1005:C1005"/>
-    <mergeCell ref="A145:C145"/>
-    <mergeCell ref="A24:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="B179:C179"/>
-    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B14988:C14988"/>
+    <mergeCell ref="B15047:C15047"/>
+    <mergeCell ref="C14816:C14817"/>
+    <mergeCell ref="B14870:C14870"/>
+    <mergeCell ref="C14523:C14524"/>
+    <mergeCell ref="B14516:C14516"/>
+    <mergeCell ref="B14457:C14457"/>
+    <mergeCell ref="B14575:C14575"/>
+    <mergeCell ref="B14585:B14587"/>
+    <mergeCell ref="B14589:B14591"/>
+    <mergeCell ref="B13631:C13631"/>
+    <mergeCell ref="C13935:C13936"/>
+    <mergeCell ref="B14044:C14044"/>
+    <mergeCell ref="C14166:C14167"/>
+    <mergeCell ref="B14221:C14221"/>
+    <mergeCell ref="C14464:C14465"/>
+    <mergeCell ref="C13223:C13224"/>
+    <mergeCell ref="B13277:C13277"/>
+    <mergeCell ref="C12581:C12582"/>
+    <mergeCell ref="B13100:C13100"/>
+    <mergeCell ref="C13172:C13173"/>
+    <mergeCell ref="C13463:C13464"/>
+    <mergeCell ref="B13291:B13293"/>
+    <mergeCell ref="C12576:C12577"/>
+    <mergeCell ref="B12628:C12628"/>
+    <mergeCell ref="C12635:C12636"/>
+    <mergeCell ref="B12510:C12510"/>
+    <mergeCell ref="B12520:B12522"/>
+    <mergeCell ref="C12405:C12406"/>
+    <mergeCell ref="B12451:C12451"/>
+    <mergeCell ref="C12468:C12469"/>
+    <mergeCell ref="C13056:C13057"/>
+    <mergeCell ref="C12820:C12821"/>
+    <mergeCell ref="B12982:C12982"/>
+    <mergeCell ref="B12994:B12996"/>
+    <mergeCell ref="B12687:C12687"/>
+    <mergeCell ref="B12701:B12703"/>
+    <mergeCell ref="B12697:B12699"/>
+    <mergeCell ref="C12708:C12709"/>
+    <mergeCell ref="C12278:C12279"/>
+    <mergeCell ref="B12333:C12333"/>
+    <mergeCell ref="C12352:C12353"/>
+    <mergeCell ref="C12106:C12107"/>
+    <mergeCell ref="B12156:C12156"/>
+    <mergeCell ref="C12226:C12227"/>
+    <mergeCell ref="C11758:C11759"/>
+    <mergeCell ref="C11866:C11867"/>
+    <mergeCell ref="C12047:C12048"/>
     <mergeCell ref="C8800:C8801"/>
     <mergeCell ref="C11516:C11517"/>
     <mergeCell ref="C11575:C11576"/>
@@ -54612,54 +54549,117 @@
     <mergeCell ref="B8921:B8923"/>
     <mergeCell ref="C8859:C8860"/>
     <mergeCell ref="B8911:C8911"/>
-    <mergeCell ref="C12278:C12279"/>
-    <mergeCell ref="B12333:C12333"/>
-    <mergeCell ref="C12352:C12353"/>
-    <mergeCell ref="C12106:C12107"/>
-    <mergeCell ref="B12156:C12156"/>
-    <mergeCell ref="C12226:C12227"/>
-    <mergeCell ref="C11758:C11759"/>
-    <mergeCell ref="C11866:C11867"/>
-    <mergeCell ref="C12047:C12048"/>
-    <mergeCell ref="C12576:C12577"/>
-    <mergeCell ref="B12628:C12628"/>
-    <mergeCell ref="C12635:C12636"/>
-    <mergeCell ref="B12510:C12510"/>
-    <mergeCell ref="B12520:B12522"/>
-    <mergeCell ref="C12405:C12406"/>
-    <mergeCell ref="B12451:C12451"/>
-    <mergeCell ref="C12468:C12469"/>
-    <mergeCell ref="C13056:C13057"/>
-    <mergeCell ref="C12820:C12821"/>
-    <mergeCell ref="B12982:C12982"/>
-    <mergeCell ref="B12994:B12996"/>
-    <mergeCell ref="B12687:C12687"/>
-    <mergeCell ref="B12701:B12703"/>
-    <mergeCell ref="B12697:B12699"/>
-    <mergeCell ref="C12708:C12709"/>
-    <mergeCell ref="B13631:C13631"/>
-    <mergeCell ref="C13935:C13936"/>
-    <mergeCell ref="B14044:C14044"/>
-    <mergeCell ref="C14166:C14167"/>
-    <mergeCell ref="B14221:C14221"/>
-    <mergeCell ref="C14464:C14465"/>
-    <mergeCell ref="C13223:C13224"/>
-    <mergeCell ref="B13277:C13277"/>
-    <mergeCell ref="C12581:C12582"/>
-    <mergeCell ref="B13100:C13100"/>
-    <mergeCell ref="C13172:C13173"/>
-    <mergeCell ref="C13463:C13464"/>
-    <mergeCell ref="B13291:B13293"/>
-    <mergeCell ref="B14988:C14988"/>
-    <mergeCell ref="B15047:C15047"/>
-    <mergeCell ref="C14816:C14817"/>
-    <mergeCell ref="B14870:C14870"/>
-    <mergeCell ref="C14523:C14524"/>
-    <mergeCell ref="B14516:C14516"/>
-    <mergeCell ref="B14457:C14457"/>
-    <mergeCell ref="B14575:C14575"/>
-    <mergeCell ref="B14585:B14587"/>
-    <mergeCell ref="B14589:B14591"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B1182:C1182"/>
+    <mergeCell ref="B1005:C1005"/>
+    <mergeCell ref="A145:C145"/>
+    <mergeCell ref="A24:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="B179:C179"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="B1477:C1477"/>
+    <mergeCell ref="B1359:C1359"/>
+    <mergeCell ref="B1300:C1300"/>
+    <mergeCell ref="B887:C887"/>
+    <mergeCell ref="C950:C951"/>
+    <mergeCell ref="B1064:C1064"/>
+    <mergeCell ref="C1248:C1249"/>
+    <mergeCell ref="C367:C368"/>
+    <mergeCell ref="B415:C415"/>
+    <mergeCell ref="B710:C710"/>
+    <mergeCell ref="B828:C828"/>
+    <mergeCell ref="C839:C840"/>
+    <mergeCell ref="C1307:C1308"/>
+    <mergeCell ref="C1314:C1315"/>
+    <mergeCell ref="B1369:B1371"/>
+    <mergeCell ref="B1373:B1375"/>
+    <mergeCell ref="B1123:C1123"/>
+    <mergeCell ref="C2255:C2256"/>
+    <mergeCell ref="B2244:C2244"/>
+    <mergeCell ref="B1949:C1949"/>
+    <mergeCell ref="B1890:C1890"/>
+    <mergeCell ref="B1831:C1831"/>
+    <mergeCell ref="B1772:C1772"/>
+    <mergeCell ref="B1713:C1713"/>
+    <mergeCell ref="C1787:C1788"/>
+    <mergeCell ref="B1654:C1654"/>
+    <mergeCell ref="B1963:B1965"/>
+    <mergeCell ref="B2775:C2775"/>
+    <mergeCell ref="C2838:C2839"/>
+    <mergeCell ref="B2893:C2893"/>
+    <mergeCell ref="B2657:C2657"/>
+    <mergeCell ref="B2716:C2716"/>
+    <mergeCell ref="C2727:C2728"/>
+    <mergeCell ref="C3202:C3203"/>
+    <mergeCell ref="B3188:C3188"/>
+    <mergeCell ref="C3077:C3078"/>
+    <mergeCell ref="C3136:C3137"/>
+    <mergeCell ref="C3195:C3196"/>
+    <mergeCell ref="B3011:C3011"/>
+    <mergeCell ref="B3365:C3365"/>
+    <mergeCell ref="C3675:C3676"/>
+    <mergeCell ref="B3257:B3259"/>
+    <mergeCell ref="B3261:B3263"/>
+    <mergeCell ref="B3247:C3247"/>
+    <mergeCell ref="B4604:C4604"/>
+    <mergeCell ref="B4663:C4663"/>
+    <mergeCell ref="C4726:C4727"/>
+    <mergeCell ref="B3660:C3660"/>
+    <mergeCell ref="B3837:C3837"/>
+    <mergeCell ref="B3896:C3896"/>
+    <mergeCell ref="C4143:C4144"/>
+    <mergeCell ref="B4191:C4191"/>
+    <mergeCell ref="B4014:C4014"/>
+    <mergeCell ref="C4025:C4026"/>
+    <mergeCell ref="B4132:C4132"/>
+    <mergeCell ref="B3851:B3853"/>
+    <mergeCell ref="C5024:C5025"/>
+    <mergeCell ref="B4781:C4781"/>
+    <mergeCell ref="C4969:C4970"/>
+    <mergeCell ref="B4899:C4899"/>
+    <mergeCell ref="C4615:C4616"/>
+    <mergeCell ref="B5135:C5135"/>
+    <mergeCell ref="B5145:B5147"/>
+    <mergeCell ref="B5149:B5151"/>
+    <mergeCell ref="B5076:C5076"/>
+    <mergeCell ref="C5083:C5084"/>
+    <mergeCell ref="C5090:C5091"/>
+    <mergeCell ref="B5607:C5607"/>
+    <mergeCell ref="B5430:C5430"/>
+    <mergeCell ref="B5489:C5489"/>
+    <mergeCell ref="B5548:C5548"/>
+    <mergeCell ref="C5563:C5564"/>
+    <mergeCell ref="B6669:C6669"/>
+    <mergeCell ref="B6787:C6787"/>
+    <mergeCell ref="C6031:C6032"/>
+    <mergeCell ref="B6492:C6492"/>
+    <mergeCell ref="C6503:C6504"/>
+    <mergeCell ref="C6614:C6615"/>
+    <mergeCell ref="B5739:B5741"/>
+    <mergeCell ref="B5725:C5725"/>
+    <mergeCell ref="C8741:C8742"/>
+    <mergeCell ref="B7627:B7629"/>
+    <mergeCell ref="C8502:C8503"/>
+    <mergeCell ref="B8557:C8557"/>
+    <mergeCell ref="B8675:C8675"/>
+    <mergeCell ref="B7613:C7613"/>
+    <mergeCell ref="B5784:C5784"/>
+    <mergeCell ref="B7672:C7672"/>
+    <mergeCell ref="B6020:C6020"/>
+    <mergeCell ref="C6853:C6854"/>
+    <mergeCell ref="C6912:C6913"/>
+    <mergeCell ref="C6971:C6972"/>
+    <mergeCell ref="B6964:C6964"/>
+    <mergeCell ref="C7451:C7452"/>
+    <mergeCell ref="B7436:C7436"/>
+    <mergeCell ref="C7558:C7559"/>
+    <mergeCell ref="B7209:B7211"/>
+    <mergeCell ref="B7318:C7318"/>
+    <mergeCell ref="C6978:C6979"/>
+    <mergeCell ref="B7023:C7023"/>
+    <mergeCell ref="B7033:B7035"/>
+    <mergeCell ref="B7037:B7039"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>
